--- a/Y英雄齿轮养成表.xlsx
+++ b/Y英雄齿轮养成表.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12345"/>
+    <workbookView windowWidth="28245" windowHeight="12345"/>
   </bookViews>
   <sheets>
     <sheet name="Data_HeroGearCfg" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1433" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="274">
   <si>
     <t>ID</t>
   </si>
@@ -238,6 +238,15 @@
   </si>
   <si>
     <t>121</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>124</t>
   </si>
   <si>
     <t>齿轮ID</t>
@@ -839,10 +848,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="29">
     <font>
@@ -909,14 +918,73 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -954,83 +1022,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1049,6 +1043,21 @@
       <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1109,7 +1118,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1121,13 +1274,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1139,157 +1298,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1374,6 +1383,30 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -1385,15 +1418,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1416,8 +1440,17 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1447,40 +1480,16 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1489,133 +1498,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2063,7 +2072,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="20.25" customWidth="1"/>
@@ -2736,6 +2745,266 @@
         <v>71</v>
       </c>
       <c r="H26" s="32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" ht="18.6" customHeight="1" spans="1:8">
+      <c r="A27" s="24">
+        <v>120</v>
+      </c>
+      <c r="B27" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="E27" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="F27" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="G27" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="H27" s="32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" ht="18.6" customHeight="1" spans="1:8">
+      <c r="A28" s="24">
+        <v>120</v>
+      </c>
+      <c r="B28" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="D28" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="E28" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="F28" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="G28" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="H28" s="32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" ht="18.6" customHeight="1" spans="1:8">
+      <c r="A29" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B29" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="D29" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="E29" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="G29" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="H29" s="32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" ht="18.6" customHeight="1" spans="1:8">
+      <c r="A30" s="24">
+        <v>120</v>
+      </c>
+      <c r="B30" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="D30" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="E30" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="F30" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="G30" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="H30" s="32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" ht="18.6" customHeight="1" spans="1:8">
+      <c r="A31" s="24">
+        <v>120</v>
+      </c>
+      <c r="B31" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="D31" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="E31" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="F31" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="G31" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="H31" s="32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" ht="18.6" customHeight="1" spans="1:8">
+      <c r="A32" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="B32" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="D32" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="E32" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="F32" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="G32" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="H32" s="32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" ht="18.6" customHeight="1" spans="1:8">
+      <c r="A33" s="24">
+        <v>120</v>
+      </c>
+      <c r="B33" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="E33" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="F33" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="G33" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="H33" s="32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" ht="18.6" customHeight="1" spans="1:8">
+      <c r="A34" s="24">
+        <v>120</v>
+      </c>
+      <c r="B34" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="D34" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="E34" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="F34" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="G34" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="H34" s="32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" ht="18.6" customHeight="1" spans="1:8">
+      <c r="A35" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B35" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="D35" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="E35" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="F35" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="G35" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="H35" s="32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" ht="18.6" customHeight="1" spans="1:8">
+      <c r="A36" s="24">
+        <v>120</v>
+      </c>
+      <c r="B36" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C36" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="D36" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="E36" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="F36" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="G36" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="H36" s="32">
         <v>100</v>
       </c>
     </row>
@@ -2759,16 +3028,16 @@
   <sheetData>
     <row r="1" ht="16.5" customHeight="1" spans="1:4">
       <c r="A1" s="21" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:4">
@@ -2787,7 +3056,7 @@
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:4">
       <c r="A3" s="21" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
@@ -2798,49 +3067,49 @@
         <v>0</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" ht="16.5" customHeight="1" spans="1:4">
       <c r="A5" s="23" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" ht="16.5" customHeight="1" spans="2:4">
       <c r="B6" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" ht="16.5" customHeight="1" spans="2:4">
       <c r="B7" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="8" ht="16.5" customHeight="1" spans="1:4">
@@ -2848,71 +3117,71 @@
         <v>102</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" ht="16.5" customHeight="1" spans="2:4">
       <c r="B9" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" ht="16.5" customHeight="1" spans="2:4">
       <c r="B10" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D10" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D10" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="11" ht="16.5" customHeight="1" spans="1:4">
       <c r="A11" s="23" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" ht="16.5" customHeight="1" spans="2:4">
       <c r="B12" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" ht="16.5" customHeight="1" spans="2:4">
       <c r="B13" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C13" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D13" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="14" ht="16.5" customHeight="1" spans="1:4">
@@ -2920,71 +3189,71 @@
         <v>103</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" ht="16.5" customHeight="1" spans="2:4">
       <c r="B15" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D15" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" ht="16.5" customHeight="1" spans="2:4">
       <c r="B16" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C16" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D16" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="17" ht="16.5" customHeight="1" spans="1:4">
       <c r="A17" s="23" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" ht="16.5" customHeight="1" spans="2:4">
       <c r="B18" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C18" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" ht="16.5" customHeight="1" spans="2:4">
       <c r="B19" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C19" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D19" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="20" ht="16.5" customHeight="1" spans="1:4">
@@ -2992,71 +3261,71 @@
         <v>104</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" ht="16.5" customHeight="1" spans="2:4">
       <c r="B21" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D21" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1" spans="2:4">
       <c r="B22" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D22" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C22" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D22" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="23" ht="16.5" customHeight="1" spans="1:4">
       <c r="A23" s="23" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D23" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" ht="16.5" customHeight="1" spans="2:4">
       <c r="B24" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D24" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" ht="16.5" customHeight="1" spans="2:4">
       <c r="B25" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D25" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C25" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D25" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="26" ht="16.5" customHeight="1" spans="1:4">
@@ -3064,71 +3333,71 @@
         <v>105</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D26" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" ht="16.5" customHeight="1" spans="2:4">
       <c r="B27" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D27" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" ht="16.5" customHeight="1" spans="2:4">
       <c r="B28" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D28" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C28" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D28" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="29" ht="16.5" customHeight="1" spans="1:4">
       <c r="A29" s="23" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B29" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C29" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D29" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" ht="16.5" customHeight="1" spans="2:4">
       <c r="B30" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C30" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D30" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" ht="16.5" customHeight="1" spans="2:4">
       <c r="B31" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C31" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D31" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C31" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D31" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="32" ht="16.5" customHeight="1" spans="1:4">
@@ -3136,71 +3405,71 @@
         <v>106</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C32" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D32" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" ht="16.5" customHeight="1" spans="2:4">
       <c r="B33" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D33" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" ht="16.5" customHeight="1" spans="2:4">
       <c r="B34" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C34" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D34" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C34" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D34" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="35" ht="16.5" customHeight="1" spans="1:4">
       <c r="A35" s="23" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B35" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" ht="16.5" customHeight="1" spans="2:4">
       <c r="B36" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C36" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D36" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" ht="16.5" customHeight="1" spans="2:4">
       <c r="B37" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C37" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D37" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C37" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D37" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="38" ht="16.5" customHeight="1" spans="1:4">
@@ -3208,71 +3477,71 @@
         <v>107</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C38" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D38" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39" ht="16.5" customHeight="1" spans="2:4">
       <c r="B39" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C39" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D39" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40" ht="16.5" customHeight="1" spans="2:4">
       <c r="B40" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C40" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D40" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C40" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D40" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="41" ht="16.5" customHeight="1" spans="1:4">
       <c r="A41" s="23" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C41" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D41" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" ht="16.5" customHeight="1" spans="2:4">
       <c r="B42" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C42" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D42" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="43" ht="16.5" customHeight="1" spans="2:4">
       <c r="B43" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C43" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D43" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C43" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D43" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="44" ht="16.5" customHeight="1" spans="1:4">
@@ -3280,71 +3549,71 @@
         <v>108</v>
       </c>
       <c r="B44" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C44" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D44" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="45" ht="16.5" customHeight="1" spans="2:4">
       <c r="B45" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C45" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D45" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="46" ht="16.5" customHeight="1" spans="2:4">
       <c r="B46" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C46" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D46" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C46" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D46" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="47" ht="16.5" customHeight="1" spans="1:4">
       <c r="A47" s="23" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B47" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C47" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D47" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="48" ht="16.5" customHeight="1" spans="2:4">
       <c r="B48" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C48" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D48" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="49" ht="16.5" customHeight="1" spans="2:4">
       <c r="B49" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C49" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D49" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C49" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D49" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="50" ht="16.5" customHeight="1" spans="1:4">
@@ -3352,71 +3621,71 @@
         <v>109</v>
       </c>
       <c r="B50" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C50" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D50" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="51" ht="16.5" customHeight="1" spans="2:4">
       <c r="B51" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C51" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D51" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="52" ht="16.5" customHeight="1" spans="2:4">
       <c r="B52" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C52" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D52" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C52" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D52" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="53" ht="16.5" customHeight="1" spans="1:4">
       <c r="A53" s="23" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B53" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C53" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D53" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="54" ht="16.5" customHeight="1" spans="2:4">
       <c r="B54" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C54" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D54" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="55" ht="16.5" customHeight="1" spans="2:4">
       <c r="B55" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C55" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D55" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C55" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D55" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="56" ht="16.5" customHeight="1" spans="1:4">
@@ -3424,71 +3693,71 @@
         <v>110</v>
       </c>
       <c r="B56" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C56" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D56" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="57" ht="16.5" customHeight="1" spans="2:4">
       <c r="B57" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C57" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D57" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="58" ht="16.5" customHeight="1" spans="2:4">
       <c r="B58" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C58" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D58" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C58" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D58" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="59" ht="16.5" customHeight="1" spans="1:4">
       <c r="A59" s="23" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B59" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C59" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D59" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="60" ht="16.5" customHeight="1" spans="2:4">
       <c r="B60" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C60" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D60" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="61" ht="16.5" customHeight="1" spans="2:4">
       <c r="B61" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C61" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D61" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C61" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D61" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="62" ht="16.5" customHeight="1" spans="1:4">
@@ -3496,71 +3765,71 @@
         <v>111</v>
       </c>
       <c r="B62" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C62" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D62" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="63" ht="16.5" customHeight="1" spans="2:4">
       <c r="B63" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C63" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D63" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="64" ht="16.5" customHeight="1" spans="2:4">
       <c r="B64" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C64" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D64" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C64" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D64" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="65" ht="16.5" customHeight="1" spans="1:4">
       <c r="A65" s="23" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B65" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C65" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D65" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="66" ht="16.5" customHeight="1" spans="2:4">
       <c r="B66" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C66" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D66" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="67" ht="16.5" customHeight="1" spans="2:4">
       <c r="B67" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C67" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D67" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C67" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D67" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="68" ht="16.5" customHeight="1" spans="1:4">
@@ -3568,71 +3837,71 @@
         <v>112</v>
       </c>
       <c r="B68" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C68" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D68" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="69" ht="16.5" customHeight="1" spans="2:4">
       <c r="B69" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C69" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D69" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="70" ht="16.5" customHeight="1" spans="2:4">
       <c r="B70" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C70" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D70" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C70" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D70" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="71" ht="16.5" customHeight="1" spans="1:4">
       <c r="A71" s="23" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B71" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C71" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D71" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="72" ht="16.5" customHeight="1" spans="2:4">
       <c r="B72" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C72" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D72" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="73" ht="16.5" customHeight="1" spans="2:4">
       <c r="B73" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C73" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D73" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C73" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D73" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="74" ht="16.5" customHeight="1" spans="1:4">
@@ -3640,71 +3909,71 @@
         <v>113</v>
       </c>
       <c r="B74" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C74" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D74" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="75" ht="16.5" customHeight="1" spans="2:4">
       <c r="B75" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C75" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D75" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="76" ht="16.5" customHeight="1" spans="2:4">
       <c r="B76" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C76" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D76" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C76" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D76" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="77" ht="16.5" customHeight="1" spans="1:4">
       <c r="A77" s="23" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B77" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C77" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D77" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="78" ht="16.5" customHeight="1" spans="2:4">
       <c r="B78" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C78" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D78" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="79" ht="16.5" customHeight="1" spans="2:4">
       <c r="B79" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C79" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D79" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C79" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D79" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="80" ht="16.5" customHeight="1" spans="1:4">
@@ -3712,71 +3981,71 @@
         <v>114</v>
       </c>
       <c r="B80" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C80" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D80" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="81" ht="16.5" customHeight="1" spans="2:4">
       <c r="B81" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C81" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D81" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="82" ht="16.5" customHeight="1" spans="2:4">
       <c r="B82" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C82" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D82" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C82" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D82" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="83" ht="16.5" customHeight="1" spans="1:4">
       <c r="A83" s="23" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B83" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C83" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D83" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="84" ht="16.5" customHeight="1" spans="2:4">
       <c r="B84" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C84" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D84" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="85" ht="16.5" customHeight="1" spans="2:4">
       <c r="B85" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C85" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D85" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C85" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D85" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="86" ht="16.5" customHeight="1" spans="1:4">
@@ -3784,71 +4053,71 @@
         <v>115</v>
       </c>
       <c r="B86" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C86" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D86" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="87" ht="16.5" customHeight="1" spans="2:4">
       <c r="B87" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C87" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D87" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="88" ht="16.5" customHeight="1" spans="2:4">
       <c r="B88" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C88" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D88" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C88" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D88" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="89" ht="16.5" customHeight="1" spans="1:4">
       <c r="A89" s="23" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B89" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C89" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D89" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="90" ht="16.5" customHeight="1" spans="2:4">
       <c r="B90" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C90" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D90" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="91" ht="16.5" customHeight="1" spans="2:4">
       <c r="B91" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C91" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D91" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C91" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D91" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="92" ht="16.5" customHeight="1" spans="1:4">
@@ -3856,71 +4125,71 @@
         <v>116</v>
       </c>
       <c r="B92" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C92" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D92" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="93" ht="16.5" customHeight="1" spans="2:4">
       <c r="B93" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C93" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D93" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="94" ht="16.5" customHeight="1" spans="2:4">
       <c r="B94" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C94" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D94" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C94" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D94" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="95" ht="16.5" customHeight="1" spans="1:4">
       <c r="A95" s="23" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B95" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C95" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D95" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="96" ht="16.5" customHeight="1" spans="2:4">
       <c r="B96" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C96" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D96" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="97" ht="16.5" customHeight="1" spans="2:4">
       <c r="B97" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C97" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D97" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C97" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D97" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="98" ht="16.5" customHeight="1" spans="1:4">
@@ -3928,71 +4197,71 @@
         <v>117</v>
       </c>
       <c r="B98" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C98" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D98" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="99" ht="16.5" customHeight="1" spans="2:4">
       <c r="B99" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C99" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D99" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="100" ht="16.5" customHeight="1" spans="2:4">
       <c r="B100" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C100" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D100" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C100" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D100" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="101" ht="16.5" customHeight="1" spans="1:4">
       <c r="A101" s="23" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B101" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C101" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D101" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="102" ht="16.5" customHeight="1" spans="2:4">
       <c r="B102" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C102" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D102" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="103" ht="16.5" customHeight="1" spans="2:4">
       <c r="B103" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C103" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D103" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C103" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D103" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="104" ht="16.5" customHeight="1" spans="1:4">
@@ -4000,71 +4269,71 @@
         <v>118</v>
       </c>
       <c r="B104" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C104" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D104" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="105" ht="16.5" customHeight="1" spans="2:4">
       <c r="B105" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C105" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D105" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="106" ht="16.5" customHeight="1" spans="2:4">
       <c r="B106" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C106" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D106" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C106" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D106" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="107" ht="16.5" customHeight="1" spans="1:4">
       <c r="A107" s="23" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B107" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C107" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D107" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="108" ht="16.5" customHeight="1" spans="2:4">
       <c r="B108" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C108" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D108" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="109" ht="16.5" customHeight="1" spans="2:4">
       <c r="B109" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C109" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D109" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C109" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D109" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="110" ht="16.5" customHeight="1" spans="1:4">
@@ -4072,71 +4341,71 @@
         <v>119</v>
       </c>
       <c r="B110" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C110" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D110" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="111" ht="16.5" customHeight="1" spans="2:4">
       <c r="B111" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C111" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D111" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="112" ht="16.5" customHeight="1" spans="2:4">
       <c r="B112" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C112" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D112" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C112" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D112" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="113" ht="16.5" customHeight="1" spans="1:4">
       <c r="A113" s="23" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B113" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C113" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D113" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="114" ht="16.5" customHeight="1" spans="2:4">
       <c r="B114" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C114" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D114" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="115" ht="16.5" customHeight="1" spans="2:4">
       <c r="B115" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C115" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D115" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="C115" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D115" s="25" t="s">
-        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -4211,52 +4480,52 @@
   <sheetData>
     <row r="1" ht="18.6" customHeight="1" spans="1:16">
       <c r="A1" s="9" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="J1" s="12" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="P1" s="15" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" ht="18.6" customHeight="1" spans="1:16">
@@ -4267,43 +4536,43 @@
         <v>8</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H2" s="10" t="s">
         <v>12</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="L2" s="14" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="M2" s="14" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="N2" s="14" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="O2" s="14" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="P2" s="16" t="s">
         <v>8</v>
@@ -4311,12 +4580,12 @@
     </row>
     <row r="3" ht="18.6" customHeight="1" spans="1:16">
       <c r="A3" s="11" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="10"/>
       <c r="D3" s="10" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E3" s="10"/>
       <c r="F3" s="10"/>
@@ -4333,69 +4602,69 @@
     </row>
     <row r="4" ht="18.6" customHeight="1" spans="1:16">
       <c r="A4" s="9" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="M4" s="14" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="N4" s="14" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="O4" s="14" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="P4" s="18" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" ht="18.6" customHeight="1" spans="1:16">
       <c r="A5" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B5" s="13">
         <v>101</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>22</v>
@@ -4436,13 +4705,13 @@
         <v>22</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F6" s="12" t="s">
         <v>28</v>
@@ -4457,7 +4726,7 @@
         <v>10</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K6" s="19">
         <v>0.1</v>
@@ -4483,13 +4752,13 @@
         <v>28</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>33</v>
@@ -4528,13 +4797,13 @@
         <v>33</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F8" s="12" t="s">
         <v>38</v>
@@ -4573,13 +4842,13 @@
         <v>38</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>41</v>
@@ -4594,7 +4863,7 @@
         <v>25</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="K9" s="19">
         <v>0.1</v>
@@ -4620,16 +4889,16 @@
         <v>41</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G10" s="13">
         <v>30</v>
@@ -4641,7 +4910,7 @@
         <v>16</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="K10" s="19">
         <v>0.1</v>
@@ -4664,19 +4933,19 @@
     </row>
     <row r="11" ht="18.6" customHeight="1" spans="1:16">
       <c r="A11" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="D11" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="C11" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>153</v>
-      </c>
       <c r="E11" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="G11" s="13">
         <v>35</v>
@@ -4688,7 +4957,7 @@
         <v>14</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="K11" s="19">
         <v>0.1</v>
@@ -4711,19 +4980,19 @@
     </row>
     <row r="12" ht="18.6" customHeight="1" spans="1:16">
       <c r="A12" s="13" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="G12" s="13">
         <v>40</v>
@@ -4735,7 +5004,7 @@
         <v>12</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="K12" s="19">
         <v>0.1</v>
@@ -4758,19 +5027,19 @@
     </row>
     <row r="13" ht="18.6" customHeight="1" spans="1:16">
       <c r="A13" s="13" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="G13" s="13">
         <v>45</v>
@@ -4782,7 +5051,7 @@
         <v>10</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="K13" s="19">
         <v>0.1</v>
@@ -4805,19 +5074,19 @@
     </row>
     <row r="14" ht="18.6" customHeight="1" spans="1:16">
       <c r="A14" s="13" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G14" s="13">
         <v>50</v>
@@ -4829,7 +5098,7 @@
         <v>8</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="K14" s="19">
         <v>0.1</v>
@@ -4852,19 +5121,19 @@
     </row>
     <row r="15" ht="18.6" customHeight="1" spans="1:16">
       <c r="A15" s="13" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="G15" s="13">
         <v>55</v>
@@ -4876,7 +5145,7 @@
         <v>6</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="K15" s="19">
         <v>0.1</v>
@@ -4899,19 +5168,19 @@
     </row>
     <row r="16" ht="18.6" customHeight="1" spans="1:16">
       <c r="A16" s="13" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="G16" s="13">
         <v>60</v>
@@ -4923,7 +5192,7 @@
         <v>4</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="K16" s="19">
         <v>0</v>
@@ -4946,19 +5215,19 @@
     </row>
     <row r="17" ht="18.6" customHeight="1" spans="1:16">
       <c r="A17" s="13" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="G17" s="13">
         <v>65</v>
@@ -4991,19 +5260,19 @@
     </row>
     <row r="18" ht="18.6" customHeight="1" spans="1:16">
       <c r="A18" s="13" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G18" s="13">
         <v>70</v>
@@ -5036,19 +5305,19 @@
     </row>
     <row r="19" ht="18.6" customHeight="1" spans="1:16">
       <c r="A19" s="13" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G19" s="13">
         <v>75</v>
@@ -5081,19 +5350,19 @@
     </row>
     <row r="20" ht="18.6" customHeight="1" spans="1:16">
       <c r="A20" s="13" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="G20" s="13">
         <v>80</v>
@@ -5126,19 +5395,19 @@
     </row>
     <row r="21" ht="18.6" customHeight="1" spans="1:16">
       <c r="A21" s="13" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="G21" s="13">
         <v>100</v>
@@ -5171,19 +5440,19 @@
     </row>
     <row r="22" ht="18.6" customHeight="1" spans="1:16">
       <c r="A22" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="D22" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>175</v>
-      </c>
       <c r="E22" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G22" s="13">
         <v>120</v>
@@ -5192,7 +5461,7 @@
         <v>22</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="J22" s="12"/>
       <c r="K22" s="19">
@@ -5216,19 +5485,19 @@
     </row>
     <row r="23" ht="18.6" customHeight="1" spans="1:16">
       <c r="A23" s="13" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G23" s="13">
         <v>140</v>
@@ -5261,19 +5530,19 @@
     </row>
     <row r="24" ht="18.6" customHeight="1" spans="1:16">
       <c r="A24" s="13" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="G24" s="13">
         <v>160</v>
@@ -5282,7 +5551,7 @@
         <v>22</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J24" s="12"/>
       <c r="K24" s="19">
@@ -5306,19 +5575,19 @@
     </row>
     <row r="25" ht="18.6" customHeight="1" spans="1:16">
       <c r="A25" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B25" s="13">
         <v>102</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F25" s="12" t="s">
         <v>22</v>
@@ -5330,10 +5599,10 @@
         <v>1</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="J25" s="20" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K25" s="19">
         <v>0</v>
@@ -5359,13 +5628,13 @@
         <v>22</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F26" s="12" t="s">
         <v>28</v>
@@ -5380,7 +5649,7 @@
         <v>5</v>
       </c>
       <c r="J26" s="20" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="K26" s="19">
         <v>0</v>
@@ -5406,13 +5675,13 @@
         <v>28</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F27" s="12" t="s">
         <v>33</v>
@@ -5424,10 +5693,10 @@
         <v>22</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="J27" s="20" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="K27" s="19">
         <v>0</v>
@@ -5453,13 +5722,13 @@
         <v>33</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F28" s="12" t="s">
         <v>38</v>
@@ -5471,10 +5740,10 @@
         <v>22</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J28" s="20" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="K28" s="19">
         <v>0</v>
@@ -5500,13 +5769,13 @@
         <v>38</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F29" s="12" t="s">
         <v>41</v>
@@ -5521,7 +5790,7 @@
         <v>6</v>
       </c>
       <c r="J29" s="20" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="K29" s="19">
         <v>0</v>
@@ -5547,16 +5816,16 @@
         <v>41</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G30" s="13">
         <v>30</v>
@@ -5565,10 +5834,10 @@
         <v>1</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J30" s="20" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="K30" s="19">
         <v>0</v>
@@ -5591,19 +5860,19 @@
     </row>
     <row r="31" ht="18.6" customHeight="1" spans="1:16">
       <c r="A31" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="D31" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>153</v>
-      </c>
       <c r="E31" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="G31" s="13">
         <v>35</v>
@@ -5612,10 +5881,10 @@
         <v>1</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="J31" s="20" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K31" s="19">
         <v>0</v>
@@ -5638,19 +5907,19 @@
     </row>
     <row r="32" ht="18.6" customHeight="1" spans="1:16">
       <c r="A32" s="13" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="G32" s="13">
         <v>40</v>
@@ -5662,7 +5931,7 @@
         <v>7</v>
       </c>
       <c r="J32" s="20" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="K32" s="19">
         <v>0</v>
@@ -5685,19 +5954,19 @@
     </row>
     <row r="33" ht="18.6" customHeight="1" spans="1:16">
       <c r="A33" s="13" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="G33" s="13">
         <v>45</v>
@@ -5706,10 +5975,10 @@
         <v>22</v>
       </c>
       <c r="I33" s="13" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J33" s="20" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K33" s="19">
         <v>0</v>
@@ -5732,19 +6001,19 @@
     </row>
     <row r="34" ht="18.6" customHeight="1" spans="1:16">
       <c r="A34" s="13" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G34" s="13">
         <v>50</v>
@@ -5753,10 +6022,10 @@
         <v>22</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J34" s="20" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="K34" s="19">
         <v>0</v>
@@ -5779,19 +6048,19 @@
     </row>
     <row r="35" ht="18.6" customHeight="1" spans="1:16">
       <c r="A35" s="13" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="G35" s="13">
         <v>55</v>
@@ -5803,7 +6072,7 @@
         <v>8</v>
       </c>
       <c r="J35" s="20" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="K35" s="19">
         <v>0</v>
@@ -5826,19 +6095,19 @@
     </row>
     <row r="36" ht="18.6" customHeight="1" spans="1:16">
       <c r="A36" s="13" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="G36" s="13">
         <v>60</v>
@@ -5847,10 +6116,10 @@
         <v>1</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J36" s="20" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="K36" s="19">
         <v>0</v>
@@ -5873,19 +6142,19 @@
     </row>
     <row r="37" ht="18.6" customHeight="1" spans="1:16">
       <c r="A37" s="13" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="G37" s="13">
         <v>65</v>
@@ -5894,10 +6163,10 @@
         <v>22</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="J37" s="20" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="K37" s="19">
         <v>0</v>
@@ -5920,19 +6189,19 @@
     </row>
     <row r="38" ht="18.6" customHeight="1" spans="1:16">
       <c r="A38" s="13" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G38" s="13">
         <v>70</v>
@@ -5965,19 +6234,19 @@
     </row>
     <row r="39" ht="18.6" customHeight="1" spans="1:16">
       <c r="A39" s="13" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G39" s="13">
         <v>75</v>
@@ -5986,7 +6255,7 @@
         <v>22</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="J39" s="12"/>
       <c r="K39" s="19">
@@ -6010,19 +6279,19 @@
     </row>
     <row r="40" ht="18.6" customHeight="1" spans="1:16">
       <c r="A40" s="13" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="G40" s="13">
         <v>80</v>
@@ -6031,7 +6300,7 @@
         <v>1</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="J40" s="12"/>
       <c r="K40" s="19">
@@ -6055,19 +6324,19 @@
     </row>
     <row r="41" ht="18.6" customHeight="1" spans="1:16">
       <c r="A41" s="13" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="G41" s="13">
         <v>100</v>
@@ -6100,19 +6369,19 @@
     </row>
     <row r="42" ht="18.6" customHeight="1" spans="1:16">
       <c r="A42" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="D42" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="C42" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="D42" s="12" t="s">
-        <v>175</v>
-      </c>
       <c r="E42" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G42" s="13">
         <v>120</v>
@@ -6121,7 +6390,7 @@
         <v>22</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="J42" s="12"/>
       <c r="K42" s="19">
@@ -6145,19 +6414,19 @@
     </row>
     <row r="43" ht="18.6" customHeight="1" spans="1:16">
       <c r="A43" s="13" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G43" s="13">
         <v>140</v>
@@ -6166,7 +6435,7 @@
         <v>22</v>
       </c>
       <c r="I43" s="13" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="J43" s="12"/>
       <c r="K43" s="19">
@@ -6190,19 +6459,19 @@
     </row>
     <row r="44" ht="18.6" customHeight="1" spans="1:16">
       <c r="A44" s="13" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="G44" s="13">
         <v>160</v>
@@ -6235,16 +6504,16 @@
     </row>
     <row r="45" ht="18.6" customHeight="1" spans="1:16">
       <c r="A45" s="13" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F45" s="12" t="s">
         <v>22</v>
@@ -6256,7 +6525,7 @@
         <v>1</v>
       </c>
       <c r="I45" s="13" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="J45" s="12"/>
       <c r="K45" s="19">
@@ -6280,19 +6549,19 @@
     </row>
     <row r="46" ht="18.6" customHeight="1" spans="1:16">
       <c r="A46" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B46" s="13">
         <v>103</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F46" s="12" t="s">
         <v>28</v>
@@ -6304,7 +6573,7 @@
         <v>1</v>
       </c>
       <c r="I46" s="13" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="J46" s="12"/>
       <c r="K46" s="19">
@@ -6331,13 +6600,13 @@
         <v>22</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F47" s="12" t="s">
         <v>33</v>
@@ -6376,13 +6645,13 @@
         <v>28</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F48" s="12" t="s">
         <v>38</v>
@@ -6394,7 +6663,7 @@
         <v>22</v>
       </c>
       <c r="I48" s="13" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="J48" s="12"/>
       <c r="K48" s="19">
@@ -6421,13 +6690,13 @@
         <v>33</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F49" s="12" t="s">
         <v>41</v>
@@ -6439,7 +6708,7 @@
         <v>22</v>
       </c>
       <c r="I49" s="13" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="J49" s="12"/>
       <c r="K49" s="19">
@@ -6466,13 +6735,13 @@
         <v>38</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F50" s="12" t="s">
         <v>22</v>
@@ -6508,19 +6777,19 @@
     </row>
     <row r="51" ht="18.6" customHeight="1" spans="1:16">
       <c r="A51" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B51" s="13">
         <v>104</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F51" s="12" t="s">
         <v>28</v>
@@ -6532,7 +6801,7 @@
         <v>1</v>
       </c>
       <c r="I51" s="13" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="J51" s="12"/>
       <c r="K51" s="19">
@@ -6559,13 +6828,13 @@
         <v>22</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F52" s="12" t="s">
         <v>33</v>
@@ -6577,7 +6846,7 @@
         <v>22</v>
       </c>
       <c r="I52" s="13" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="J52" s="12"/>
       <c r="K52" s="19">
@@ -6604,13 +6873,13 @@
         <v>28</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F53" s="12" t="s">
         <v>38</v>
@@ -6649,13 +6918,13 @@
         <v>33</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F54" s="12" t="s">
         <v>41</v>
@@ -6667,7 +6936,7 @@
         <v>22</v>
       </c>
       <c r="I54" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="J54" s="12"/>
       <c r="K54" s="19">
@@ -6694,13 +6963,13 @@
         <v>38</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F55" s="12" t="s">
         <v>22</v>
@@ -6712,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="I55" s="13" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="J55" s="12"/>
       <c r="K55" s="19">
@@ -6736,19 +7005,19 @@
     </row>
     <row r="56" ht="18.6" customHeight="1" spans="1:16">
       <c r="A56" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B56" s="13">
         <v>105</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F56" s="12" t="s">
         <v>28</v>
@@ -6787,13 +7056,13 @@
         <v>22</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F57" s="12" t="s">
         <v>33</v>
@@ -6805,7 +7074,7 @@
         <v>22</v>
       </c>
       <c r="I57" s="13" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="J57" s="12"/>
       <c r="K57" s="19">
@@ -6832,13 +7101,13 @@
         <v>28</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F58" s="12" t="s">
         <v>38</v>
@@ -6850,7 +7119,7 @@
         <v>22</v>
       </c>
       <c r="I58" s="13" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="J58" s="12"/>
       <c r="K58" s="19">
@@ -6877,13 +7146,13 @@
         <v>33</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F59" s="12" t="s">
         <v>41</v>
@@ -6922,13 +7191,13 @@
         <v>38</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F60" s="12" t="s">
         <v>22</v>
@@ -6940,7 +7209,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="13" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="J60" s="12"/>
       <c r="K60" s="19">
@@ -6964,19 +7233,19 @@
     </row>
     <row r="61" ht="18.6" customHeight="1" spans="1:16">
       <c r="A61" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B61" s="13">
         <v>106</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F61" s="12" t="s">
         <v>28</v>
@@ -6988,7 +7257,7 @@
         <v>1</v>
       </c>
       <c r="I61" s="13" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="J61" s="12"/>
       <c r="K61" s="19">
@@ -7015,13 +7284,13 @@
         <v>22</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F62" s="12" t="s">
         <v>33</v>
@@ -7060,13 +7329,13 @@
         <v>28</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F63" s="12" t="s">
         <v>38</v>
@@ -7078,7 +7347,7 @@
         <v>22</v>
       </c>
       <c r="I63" s="13" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="J63" s="12"/>
       <c r="K63" s="19">
@@ -7105,13 +7374,13 @@
         <v>33</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F64" s="12" t="s">
         <v>41</v>
@@ -7123,7 +7392,7 @@
         <v>22</v>
       </c>
       <c r="I64" s="13" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="J64" s="12"/>
       <c r="K64" s="19">
@@ -7150,13 +7419,13 @@
         <v>38</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F65" s="12" t="s">
         <v>22</v>
@@ -7192,19 +7461,19 @@
     </row>
     <row r="66" ht="18.6" customHeight="1" spans="1:16">
       <c r="A66" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B66" s="13">
         <v>107</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F66" s="12" t="s">
         <v>28</v>
@@ -7216,7 +7485,7 @@
         <v>1</v>
       </c>
       <c r="I66" s="13" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="J66" s="12"/>
       <c r="K66" s="19">
@@ -7243,13 +7512,13 @@
         <v>22</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F67" s="12" t="s">
         <v>33</v>
@@ -7261,7 +7530,7 @@
         <v>22</v>
       </c>
       <c r="I67" s="13" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="J67" s="12"/>
       <c r="K67" s="19">
@@ -7288,13 +7557,13 @@
         <v>28</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F68" s="12" t="s">
         <v>38</v>
@@ -7333,13 +7602,13 @@
         <v>33</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F69" s="12" t="s">
         <v>41</v>
@@ -7351,7 +7620,7 @@
         <v>22</v>
       </c>
       <c r="I69" s="13" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="J69" s="12"/>
       <c r="K69" s="19">
@@ -7378,13 +7647,13 @@
         <v>38</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F70" s="12" t="s">
         <v>22</v>
@@ -7396,7 +7665,7 @@
         <v>1</v>
       </c>
       <c r="I70" s="13" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="J70" s="12"/>
       <c r="K70" s="19">
@@ -7420,19 +7689,19 @@
     </row>
     <row r="71" ht="18.6" customHeight="1" spans="1:16">
       <c r="A71" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B71" s="13">
         <v>108</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F71" s="12" t="s">
         <v>28</v>
@@ -7471,13 +7740,13 @@
         <v>22</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F72" s="12" t="s">
         <v>33</v>
@@ -7489,7 +7758,7 @@
         <v>22</v>
       </c>
       <c r="I72" s="13" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="J72" s="12"/>
       <c r="K72" s="19">
@@ -7516,13 +7785,13 @@
         <v>28</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F73" s="12" t="s">
         <v>38</v>
@@ -7534,7 +7803,7 @@
         <v>22</v>
       </c>
       <c r="I73" s="13" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="J73" s="12"/>
       <c r="K73" s="19">
@@ -7561,13 +7830,13 @@
         <v>33</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F74" s="12" t="s">
         <v>41</v>
@@ -7606,13 +7875,13 @@
         <v>38</v>
       </c>
       <c r="C75" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F75" s="12" t="s">
         <v>22</v>
@@ -7624,7 +7893,7 @@
         <v>1</v>
       </c>
       <c r="I75" s="13" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="J75" s="12"/>
       <c r="K75" s="19">
@@ -7648,19 +7917,19 @@
     </row>
     <row r="76" ht="18.6" customHeight="1" spans="1:16">
       <c r="A76" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B76" s="13">
         <v>109</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F76" s="12" t="s">
         <v>28</v>
@@ -7672,7 +7941,7 @@
         <v>1</v>
       </c>
       <c r="I76" s="13" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="J76" s="12"/>
       <c r="K76" s="19">
@@ -7699,13 +7968,13 @@
         <v>22</v>
       </c>
       <c r="C77" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F77" s="12" t="s">
         <v>33</v>
@@ -7744,13 +8013,13 @@
         <v>28</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D78" s="12" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F78" s="12" t="s">
         <v>38</v>
@@ -7762,7 +8031,7 @@
         <v>22</v>
       </c>
       <c r="I78" s="13" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="J78" s="12"/>
       <c r="K78" s="19">
@@ -7789,13 +8058,13 @@
         <v>33</v>
       </c>
       <c r="C79" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F79" s="12" t="s">
         <v>41</v>
@@ -7807,7 +8076,7 @@
         <v>22</v>
       </c>
       <c r="I79" s="13" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="J79" s="12"/>
       <c r="K79" s="19">
@@ -7834,13 +8103,13 @@
         <v>38</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F80" s="12" t="s">
         <v>22</v>
@@ -7876,19 +8145,19 @@
     </row>
     <row r="81" ht="18.6" customHeight="1" spans="1:16">
       <c r="A81" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B81" s="13">
         <v>110</v>
       </c>
       <c r="C81" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F81" s="12" t="s">
         <v>28</v>
@@ -7900,7 +8169,7 @@
         <v>1</v>
       </c>
       <c r="I81" s="13" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="J81" s="12"/>
       <c r="K81" s="19">
@@ -7927,13 +8196,13 @@
         <v>22</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D82" s="12" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F82" s="12" t="s">
         <v>33</v>
@@ -7945,7 +8214,7 @@
         <v>22</v>
       </c>
       <c r="I82" s="13" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="J82" s="12"/>
       <c r="K82" s="19">
@@ -7972,13 +8241,13 @@
         <v>28</v>
       </c>
       <c r="C83" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F83" s="12" t="s">
         <v>38</v>
@@ -8017,13 +8286,13 @@
         <v>33</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F84" s="12" t="s">
         <v>41</v>
@@ -8035,7 +8304,7 @@
         <v>22</v>
       </c>
       <c r="I84" s="13" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="J84" s="12"/>
       <c r="K84" s="19">
@@ -8062,13 +8331,13 @@
         <v>38</v>
       </c>
       <c r="C85" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F85" s="12" t="s">
         <v>22</v>
@@ -8080,7 +8349,7 @@
         <v>1</v>
       </c>
       <c r="I85" s="13" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="J85" s="12"/>
       <c r="K85" s="19">
@@ -8104,19 +8373,19 @@
     </row>
     <row r="86" ht="18.6" customHeight="1" spans="1:16">
       <c r="A86" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B86" s="13">
         <v>111</v>
       </c>
       <c r="C86" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D86" s="12" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E86" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F86" s="12" t="s">
         <v>28</v>
@@ -8155,13 +8424,13 @@
         <v>22</v>
       </c>
       <c r="C87" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F87" s="12" t="s">
         <v>33</v>
@@ -8173,7 +8442,7 @@
         <v>22</v>
       </c>
       <c r="I87" s="13" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="J87" s="12"/>
       <c r="K87" s="19">
@@ -8200,13 +8469,13 @@
         <v>28</v>
       </c>
       <c r="C88" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F88" s="12" t="s">
         <v>38</v>
@@ -8218,7 +8487,7 @@
         <v>22</v>
       </c>
       <c r="I88" s="13" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J88" s="12"/>
       <c r="K88" s="19">
@@ -8245,13 +8514,13 @@
         <v>33</v>
       </c>
       <c r="C89" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F89" s="12" t="s">
         <v>41</v>
@@ -8290,13 +8559,13 @@
         <v>38</v>
       </c>
       <c r="C90" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D90" s="12" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F90" s="12" t="s">
         <v>22</v>
@@ -8308,7 +8577,7 @@
         <v>1</v>
       </c>
       <c r="I90" s="13" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="J90" s="12"/>
       <c r="K90" s="19">
@@ -8332,19 +8601,19 @@
     </row>
     <row r="91" ht="18.6" customHeight="1" spans="1:16">
       <c r="A91" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B91" s="13">
         <v>112</v>
       </c>
       <c r="C91" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F91" s="12" t="s">
         <v>28</v>
@@ -8356,7 +8625,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="13" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J91" s="12"/>
       <c r="K91" s="19">
@@ -8383,13 +8652,13 @@
         <v>22</v>
       </c>
       <c r="C92" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D92" s="12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F92" s="12" t="s">
         <v>33</v>
@@ -8428,13 +8697,13 @@
         <v>28</v>
       </c>
       <c r="C93" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E93" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F93" s="12" t="s">
         <v>38</v>
@@ -8446,7 +8715,7 @@
         <v>22</v>
       </c>
       <c r="I93" s="13" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="J93" s="12"/>
       <c r="K93" s="19">
@@ -8473,13 +8742,13 @@
         <v>33</v>
       </c>
       <c r="C94" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D94" s="12" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E94" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F94" s="12" t="s">
         <v>41</v>
@@ -8491,7 +8760,7 @@
         <v>22</v>
       </c>
       <c r="I94" s="13" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="J94" s="12"/>
       <c r="K94" s="19">
@@ -8518,13 +8787,13 @@
         <v>38</v>
       </c>
       <c r="C95" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E95" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F95" s="12" t="s">
         <v>22</v>
@@ -8560,19 +8829,19 @@
     </row>
     <row r="96" ht="18.6" customHeight="1" spans="1:16">
       <c r="A96" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B96" s="13">
         <v>113</v>
       </c>
       <c r="C96" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D96" s="12" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E96" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F96" s="12" t="s">
         <v>28</v>
@@ -8584,7 +8853,7 @@
         <v>1</v>
       </c>
       <c r="I96" s="13" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="J96" s="12"/>
       <c r="K96" s="19">
@@ -8611,13 +8880,13 @@
         <v>22</v>
       </c>
       <c r="C97" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D97" s="12" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E97" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F97" s="12" t="s">
         <v>33</v>
@@ -8629,7 +8898,7 @@
         <v>22</v>
       </c>
       <c r="I97" s="13" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="J97" s="12"/>
       <c r="K97" s="19">
@@ -8656,13 +8925,13 @@
         <v>28</v>
       </c>
       <c r="C98" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D98" s="12" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E98" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F98" s="12" t="s">
         <v>38</v>
@@ -8701,13 +8970,13 @@
         <v>33</v>
       </c>
       <c r="C99" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D99" s="12" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E99" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F99" s="12" t="s">
         <v>41</v>
@@ -8719,7 +8988,7 @@
         <v>22</v>
       </c>
       <c r="I99" s="13" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="J99" s="12"/>
       <c r="K99" s="19">
@@ -8746,13 +9015,13 @@
         <v>38</v>
       </c>
       <c r="C100" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D100" s="12" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E100" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F100" s="12" t="s">
         <v>22</v>
@@ -8764,7 +9033,7 @@
         <v>1</v>
       </c>
       <c r="I100" s="13" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="J100" s="12"/>
       <c r="K100" s="19">
@@ -8788,19 +9057,19 @@
     </row>
     <row r="101" ht="18.6" customHeight="1" spans="1:16">
       <c r="A101" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B101" s="13">
         <v>114</v>
       </c>
       <c r="C101" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D101" s="12" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E101" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F101" s="12" t="s">
         <v>28</v>
@@ -8839,13 +9108,13 @@
         <v>22</v>
       </c>
       <c r="C102" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D102" s="12" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F102" s="12" t="s">
         <v>33</v>
@@ -8857,7 +9126,7 @@
         <v>22</v>
       </c>
       <c r="I102" s="13" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="J102" s="12"/>
       <c r="K102" s="19">
@@ -8884,13 +9153,13 @@
         <v>28</v>
       </c>
       <c r="C103" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D103" s="12" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F103" s="12" t="s">
         <v>38</v>
@@ -8902,7 +9171,7 @@
         <v>22</v>
       </c>
       <c r="I103" s="13" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="J103" s="12"/>
       <c r="K103" s="19">
@@ -8929,13 +9198,13 @@
         <v>33</v>
       </c>
       <c r="C104" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D104" s="12" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E104" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F104" s="12" t="s">
         <v>41</v>
@@ -8974,13 +9243,13 @@
         <v>38</v>
       </c>
       <c r="C105" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D105" s="12" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E105" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F105" s="12" t="s">
         <v>22</v>
@@ -8992,7 +9261,7 @@
         <v>1</v>
       </c>
       <c r="I105" s="13" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="J105" s="12"/>
       <c r="K105" s="19">
@@ -9016,19 +9285,19 @@
     </row>
     <row r="106" ht="18.6" customHeight="1" spans="1:16">
       <c r="A106" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B106" s="13">
         <v>115</v>
       </c>
       <c r="C106" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D106" s="12" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E106" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F106" s="12" t="s">
         <v>28</v>
@@ -9040,7 +9309,7 @@
         <v>1</v>
       </c>
       <c r="I106" s="13" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="J106" s="12"/>
       <c r="K106" s="19">
@@ -9067,13 +9336,13 @@
         <v>22</v>
       </c>
       <c r="C107" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D107" s="12" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E107" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F107" s="12" t="s">
         <v>33</v>
@@ -9112,13 +9381,13 @@
         <v>28</v>
       </c>
       <c r="C108" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D108" s="12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E108" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F108" s="12" t="s">
         <v>38</v>
@@ -9130,7 +9399,7 @@
         <v>22</v>
       </c>
       <c r="I108" s="13" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="J108" s="12"/>
       <c r="K108" s="19">
@@ -9157,13 +9426,13 @@
         <v>33</v>
       </c>
       <c r="C109" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D109" s="12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E109" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F109" s="12" t="s">
         <v>41</v>
@@ -9175,7 +9444,7 @@
         <v>22</v>
       </c>
       <c r="I109" s="13" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="J109" s="12"/>
       <c r="K109" s="19">
@@ -9202,13 +9471,13 @@
         <v>38</v>
       </c>
       <c r="C110" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D110" s="12" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E110" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F110" s="12" t="s">
         <v>22</v>
@@ -9244,19 +9513,19 @@
     </row>
     <row r="111" ht="18.6" customHeight="1" spans="1:16">
       <c r="A111" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B111" s="13">
         <v>116</v>
       </c>
       <c r="C111" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D111" s="12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E111" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F111" s="12" t="s">
         <v>28</v>
@@ -9268,7 +9537,7 @@
         <v>1</v>
       </c>
       <c r="I111" s="13" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="J111" s="12"/>
       <c r="K111" s="19">
@@ -9295,13 +9564,13 @@
         <v>22</v>
       </c>
       <c r="C112" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D112" s="12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E112" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F112" s="12" t="s">
         <v>33</v>
@@ -9313,7 +9582,7 @@
         <v>22</v>
       </c>
       <c r="I112" s="13" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="J112" s="12"/>
       <c r="K112" s="19">
@@ -9340,13 +9609,13 @@
         <v>28</v>
       </c>
       <c r="C113" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D113" s="12" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E113" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F113" s="12" t="s">
         <v>38</v>
@@ -9385,13 +9654,13 @@
         <v>33</v>
       </c>
       <c r="C114" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D114" s="12" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E114" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F114" s="12" t="s">
         <v>41</v>
@@ -9403,7 +9672,7 @@
         <v>22</v>
       </c>
       <c r="I114" s="13" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="J114" s="12"/>
       <c r="K114" s="19">
@@ -9430,13 +9699,13 @@
         <v>38</v>
       </c>
       <c r="C115" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D115" s="12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E115" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F115" s="12" t="s">
         <v>22</v>
@@ -9448,7 +9717,7 @@
         <v>1</v>
       </c>
       <c r="I115" s="13" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="J115" s="12"/>
       <c r="K115" s="19">
@@ -9472,19 +9741,19 @@
     </row>
     <row r="116" ht="18.6" customHeight="1" spans="1:16">
       <c r="A116" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B116" s="13">
         <v>117</v>
       </c>
       <c r="C116" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D116" s="12" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E116" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F116" s="12" t="s">
         <v>28</v>
@@ -9523,13 +9792,13 @@
         <v>22</v>
       </c>
       <c r="C117" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D117" s="12" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E117" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F117" s="12" t="s">
         <v>33</v>
@@ -9541,7 +9810,7 @@
         <v>22</v>
       </c>
       <c r="I117" s="13" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="J117" s="12"/>
       <c r="K117" s="19">
@@ -9568,13 +9837,13 @@
         <v>28</v>
       </c>
       <c r="C118" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D118" s="12" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E118" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F118" s="12" t="s">
         <v>38</v>
@@ -9586,7 +9855,7 @@
         <v>22</v>
       </c>
       <c r="I118" s="13" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="J118" s="12"/>
       <c r="K118" s="19">
@@ -9613,13 +9882,13 @@
         <v>33</v>
       </c>
       <c r="C119" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D119" s="12" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F119" s="12" t="s">
         <v>41</v>
@@ -9658,13 +9927,13 @@
         <v>38</v>
       </c>
       <c r="C120" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D120" s="12" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F120" s="12" t="s">
         <v>22</v>
@@ -9676,7 +9945,7 @@
         <v>1</v>
       </c>
       <c r="I120" s="13" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="J120" s="12"/>
       <c r="K120" s="19">
@@ -9700,19 +9969,19 @@
     </row>
     <row r="121" ht="18.6" customHeight="1" spans="1:16">
       <c r="A121" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B121" s="13">
         <v>118</v>
       </c>
       <c r="C121" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D121" s="12" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E121" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F121" s="12" t="s">
         <v>28</v>
@@ -9724,7 +9993,7 @@
         <v>1</v>
       </c>
       <c r="I121" s="13" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="J121" s="12"/>
       <c r="K121" s="19">
@@ -9751,13 +10020,13 @@
         <v>22</v>
       </c>
       <c r="C122" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D122" s="12" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E122" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F122" s="12" t="s">
         <v>33</v>
@@ -9796,13 +10065,13 @@
         <v>28</v>
       </c>
       <c r="C123" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D123" s="12" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E123" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F123" s="12" t="s">
         <v>38</v>
@@ -9814,7 +10083,7 @@
         <v>22</v>
       </c>
       <c r="I123" s="13" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="J123" s="12"/>
       <c r="K123" s="19">
@@ -9841,13 +10110,13 @@
         <v>33</v>
       </c>
       <c r="C124" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D124" s="12" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E124" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F124" s="12" t="s">
         <v>41</v>
@@ -9859,7 +10128,7 @@
         <v>22</v>
       </c>
       <c r="I124" s="13" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="J124" s="12"/>
       <c r="K124" s="19">
@@ -9886,13 +10155,13 @@
         <v>38</v>
       </c>
       <c r="C125" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D125" s="12" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E125" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F125" s="12" t="s">
         <v>22</v>
@@ -9928,19 +10197,19 @@
     </row>
     <row r="126" ht="18.6" customHeight="1" spans="1:16">
       <c r="A126" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B126" s="13">
         <v>119</v>
       </c>
       <c r="C126" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D126" s="12" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E126" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F126" s="12" t="s">
         <v>28</v>
@@ -9952,7 +10221,7 @@
         <v>1</v>
       </c>
       <c r="I126" s="13" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="J126" s="12"/>
       <c r="K126" s="19">
@@ -9979,13 +10248,13 @@
         <v>22</v>
       </c>
       <c r="C127" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D127" s="12" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E127" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F127" s="12" t="s">
         <v>33</v>
@@ -9997,7 +10266,7 @@
         <v>22</v>
       </c>
       <c r="I127" s="13" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="J127" s="12"/>
       <c r="K127" s="19">
@@ -10024,13 +10293,13 @@
         <v>28</v>
       </c>
       <c r="C128" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D128" s="12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E128" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F128" s="12" t="s">
         <v>38</v>
@@ -10069,13 +10338,13 @@
         <v>33</v>
       </c>
       <c r="C129" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D129" s="12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E129" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F129" s="12" t="s">
         <v>41</v>
@@ -10087,7 +10356,7 @@
         <v>22</v>
       </c>
       <c r="I129" s="13" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="J129" s="12"/>
       <c r="K129" s="19">
@@ -10114,13 +10383,13 @@
         <v>38</v>
       </c>
       <c r="C130" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D130" s="12" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E130" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F130" s="12" t="s">
         <v>22</v>
@@ -10132,7 +10401,7 @@
         <v>1</v>
       </c>
       <c r="I130" s="13" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="J130" s="12"/>
       <c r="K130" s="19">
@@ -10156,19 +10425,19 @@
     </row>
     <row r="131" ht="18.6" customHeight="1" spans="1:16">
       <c r="A131" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B131" s="13">
         <v>120</v>
       </c>
       <c r="C131" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D131" s="12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E131" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F131" s="12" t="s">
         <v>28</v>
@@ -10207,13 +10476,13 @@
         <v>22</v>
       </c>
       <c r="C132" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D132" s="12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E132" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F132" s="12" t="s">
         <v>33</v>
@@ -10225,7 +10494,7 @@
         <v>22</v>
       </c>
       <c r="I132" s="13" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="J132" s="12"/>
       <c r="K132" s="19">
@@ -10252,13 +10521,13 @@
         <v>28</v>
       </c>
       <c r="C133" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D133" s="12" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E133" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F133" s="12" t="s">
         <v>38</v>
@@ -10270,7 +10539,7 @@
         <v>22</v>
       </c>
       <c r="I133" s="13" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="J133" s="12"/>
       <c r="K133" s="19">
@@ -10297,13 +10566,13 @@
         <v>33</v>
       </c>
       <c r="C134" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D134" s="12" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E134" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F134" s="12" t="s">
         <v>41</v>
@@ -10342,16 +10611,16 @@
         <v>38</v>
       </c>
       <c r="C135" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D135" s="12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E135" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F135" s="12" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G135" s="13">
         <v>25</v>
@@ -10360,7 +10629,7 @@
         <v>1</v>
       </c>
       <c r="I135" s="13" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="J135" s="12"/>
       <c r="K135" s="19">
@@ -10422,7 +10691,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="8" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -10432,12 +10701,12 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="8" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -10472,22 +10741,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:7">
@@ -10529,22 +10798,22 @@
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:7">

--- a/Y英雄齿轮养成表.xlsx
+++ b/Y英雄齿轮养成表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1527" uniqueCount="275">
   <si>
     <t>ID</t>
   </si>
@@ -247,6 +247,9 @@
   </si>
   <si>
     <t>124</t>
+  </si>
+  <si>
+    <t>125</t>
   </si>
   <si>
     <t>齿轮ID</t>
@@ -850,8 +853,8 @@
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="29">
     <font>
@@ -926,7 +929,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -934,21 +937,6 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -962,22 +950,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -991,8 +964,23 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1003,6 +991,28 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1023,10 +1033,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1046,18 +1056,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1118,13 +1121,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1136,145 +1205,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1292,13 +1229,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1383,30 +1386,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -1418,21 +1397,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1450,7 +1414,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1480,6 +1444,45 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1489,7 +1492,7 @@
     <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1498,112 +1501,118 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="40" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="40" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1612,19 +1621,13 @@
     <xf numFmtId="0" fontId="12" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2072,7 +2075,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="20.25" customWidth="1"/>
@@ -3005,6 +3008,136 @@
         <v>71</v>
       </c>
       <c r="H36" s="32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" ht="18.6" customHeight="1" spans="1:8">
+      <c r="A37" s="24">
+        <v>120</v>
+      </c>
+      <c r="B37" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C37" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="D37" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="E37" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="F37" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="G37" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="H37" s="32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" ht="18.6" customHeight="1" spans="1:8">
+      <c r="A38" s="24">
+        <v>120</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C38" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="D38" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="E38" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="F38" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="G38" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="H38" s="32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" ht="18.6" customHeight="1" spans="1:8">
+      <c r="A39" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="B39" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C39" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="D39" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="E39" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="F39" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="G39" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="H39" s="32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" ht="18.6" customHeight="1" spans="1:8">
+      <c r="A40" s="24">
+        <v>121</v>
+      </c>
+      <c r="B40" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C40" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="D40" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="E40" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="F40" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="G40" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="H40" s="32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" ht="18.6" customHeight="1" spans="1:8">
+      <c r="A41" s="24">
+        <v>120</v>
+      </c>
+      <c r="B41" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C41" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="D41" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="E41" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="F41" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="G41" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="H41" s="32">
         <v>100</v>
       </c>
     </row>
@@ -3028,16 +3161,16 @@
   <sheetData>
     <row r="1" ht="16.5" customHeight="1" spans="1:4">
       <c r="A1" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:4">
@@ -3056,7 +3189,7 @@
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:4">
       <c r="A3" s="21" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
@@ -3067,49 +3200,49 @@
         <v>0</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" ht="16.5" customHeight="1" spans="1:4">
       <c r="A5" s="23" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" ht="16.5" customHeight="1" spans="2:4">
       <c r="B6" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C6" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D6" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="7" ht="16.5" customHeight="1" spans="2:4">
       <c r="B7" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" ht="16.5" customHeight="1" spans="1:4">
@@ -3117,71 +3250,71 @@
         <v>102</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" ht="16.5" customHeight="1" spans="2:4">
       <c r="B9" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C9" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D9" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="10" ht="16.5" customHeight="1" spans="2:4">
       <c r="B10" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" ht="16.5" customHeight="1" spans="1:4">
       <c r="A11" s="23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" ht="16.5" customHeight="1" spans="2:4">
       <c r="B12" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D12" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C12" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D12" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="13" ht="16.5" customHeight="1" spans="2:4">
       <c r="B13" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" ht="16.5" customHeight="1" spans="1:4">
@@ -3189,71 +3322,71 @@
         <v>103</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" ht="16.5" customHeight="1" spans="2:4">
       <c r="B15" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C15" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D15" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="16" ht="16.5" customHeight="1" spans="2:4">
       <c r="B16" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" ht="16.5" customHeight="1" spans="1:4">
       <c r="A17" s="23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" ht="16.5" customHeight="1" spans="2:4">
       <c r="B18" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C18" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D18" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="19" ht="16.5" customHeight="1" spans="2:4">
       <c r="B19" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C19" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D19" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" ht="16.5" customHeight="1" spans="1:4">
@@ -3261,71 +3394,71 @@
         <v>104</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" ht="16.5" customHeight="1" spans="2:4">
       <c r="B21" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C21" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D21" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1" spans="2:4">
       <c r="B22" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D22" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" ht="16.5" customHeight="1" spans="1:4">
       <c r="A23" s="23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D23" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" ht="16.5" customHeight="1" spans="2:4">
       <c r="B24" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D24" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D24" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="25" ht="16.5" customHeight="1" spans="2:4">
       <c r="B25" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D25" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" ht="16.5" customHeight="1" spans="1:4">
@@ -3333,71 +3466,71 @@
         <v>105</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D26" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" ht="16.5" customHeight="1" spans="2:4">
       <c r="B27" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D27" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C27" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D27" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="28" ht="16.5" customHeight="1" spans="2:4">
       <c r="B28" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C28" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D28" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29" ht="16.5" customHeight="1" spans="1:4">
       <c r="A29" s="23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B29" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C29" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D29" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30" ht="16.5" customHeight="1" spans="2:4">
       <c r="B30" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C30" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D30" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C30" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D30" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="31" ht="16.5" customHeight="1" spans="2:4">
       <c r="B31" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C31" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D31" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" ht="16.5" customHeight="1" spans="1:4">
@@ -3405,71 +3538,71 @@
         <v>106</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C32" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D32" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" ht="16.5" customHeight="1" spans="2:4">
       <c r="B33" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C33" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D33" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C33" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D33" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="34" ht="16.5" customHeight="1" spans="2:4">
       <c r="B34" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D34" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" ht="16.5" customHeight="1" spans="1:4">
       <c r="A35" s="23" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B35" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" ht="16.5" customHeight="1" spans="2:4">
       <c r="B36" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C36" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D36" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C36" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D36" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="37" ht="16.5" customHeight="1" spans="2:4">
       <c r="B37" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C37" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D37" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38" ht="16.5" customHeight="1" spans="1:4">
@@ -3477,71 +3610,71 @@
         <v>107</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C38" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D38" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39" ht="16.5" customHeight="1" spans="2:4">
       <c r="B39" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C39" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D39" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C39" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D39" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="40" ht="16.5" customHeight="1" spans="2:4">
       <c r="B40" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C40" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D40" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="41" ht="16.5" customHeight="1" spans="1:4">
       <c r="A41" s="23" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C41" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D41" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="42" ht="16.5" customHeight="1" spans="2:4">
       <c r="B42" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C42" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D42" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C42" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D42" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="43" ht="16.5" customHeight="1" spans="2:4">
       <c r="B43" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C43" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D43" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="44" ht="16.5" customHeight="1" spans="1:4">
@@ -3549,71 +3682,71 @@
         <v>108</v>
       </c>
       <c r="B44" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C44" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D44" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="45" ht="16.5" customHeight="1" spans="2:4">
       <c r="B45" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C45" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D45" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C45" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D45" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="46" ht="16.5" customHeight="1" spans="2:4">
       <c r="B46" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C46" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D46" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="47" ht="16.5" customHeight="1" spans="1:4">
       <c r="A47" s="23" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B47" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C47" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D47" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="48" ht="16.5" customHeight="1" spans="2:4">
       <c r="B48" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C48" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D48" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C48" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D48" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="49" ht="16.5" customHeight="1" spans="2:4">
       <c r="B49" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C49" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D49" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="50" ht="16.5" customHeight="1" spans="1:4">
@@ -3621,71 +3754,71 @@
         <v>109</v>
       </c>
       <c r="B50" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C50" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D50" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="51" ht="16.5" customHeight="1" spans="2:4">
       <c r="B51" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C51" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D51" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C51" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D51" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="52" ht="16.5" customHeight="1" spans="2:4">
       <c r="B52" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C52" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D52" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="53" ht="16.5" customHeight="1" spans="1:4">
       <c r="A53" s="23" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B53" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C53" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D53" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="54" ht="16.5" customHeight="1" spans="2:4">
       <c r="B54" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C54" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D54" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C54" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D54" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="55" ht="16.5" customHeight="1" spans="2:4">
       <c r="B55" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C55" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D55" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="56" ht="16.5" customHeight="1" spans="1:4">
@@ -3693,71 +3826,71 @@
         <v>110</v>
       </c>
       <c r="B56" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C56" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D56" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="57" ht="16.5" customHeight="1" spans="2:4">
       <c r="B57" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C57" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D57" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C57" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D57" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="58" ht="16.5" customHeight="1" spans="2:4">
       <c r="B58" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C58" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D58" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="59" ht="16.5" customHeight="1" spans="1:4">
       <c r="A59" s="23" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B59" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C59" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D59" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="60" ht="16.5" customHeight="1" spans="2:4">
       <c r="B60" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C60" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D60" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C60" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D60" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="61" ht="16.5" customHeight="1" spans="2:4">
       <c r="B61" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C61" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D61" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="62" ht="16.5" customHeight="1" spans="1:4">
@@ -3765,71 +3898,71 @@
         <v>111</v>
       </c>
       <c r="B62" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C62" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D62" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="63" ht="16.5" customHeight="1" spans="2:4">
       <c r="B63" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C63" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D63" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C63" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D63" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="64" ht="16.5" customHeight="1" spans="2:4">
       <c r="B64" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C64" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D64" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="65" ht="16.5" customHeight="1" spans="1:4">
       <c r="A65" s="23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B65" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C65" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D65" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="66" ht="16.5" customHeight="1" spans="2:4">
       <c r="B66" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C66" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D66" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C66" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D66" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="67" ht="16.5" customHeight="1" spans="2:4">
       <c r="B67" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C67" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D67" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="68" ht="16.5" customHeight="1" spans="1:4">
@@ -3837,71 +3970,71 @@
         <v>112</v>
       </c>
       <c r="B68" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C68" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D68" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="69" ht="16.5" customHeight="1" spans="2:4">
       <c r="B69" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C69" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D69" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C69" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D69" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="70" ht="16.5" customHeight="1" spans="2:4">
       <c r="B70" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C70" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D70" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="71" ht="16.5" customHeight="1" spans="1:4">
       <c r="A71" s="23" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B71" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C71" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D71" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="72" ht="16.5" customHeight="1" spans="2:4">
       <c r="B72" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C72" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D72" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C72" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D72" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="73" ht="16.5" customHeight="1" spans="2:4">
       <c r="B73" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C73" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D73" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="74" ht="16.5" customHeight="1" spans="1:4">
@@ -3909,71 +4042,71 @@
         <v>113</v>
       </c>
       <c r="B74" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C74" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D74" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="75" ht="16.5" customHeight="1" spans="2:4">
       <c r="B75" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C75" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D75" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C75" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D75" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="76" ht="16.5" customHeight="1" spans="2:4">
       <c r="B76" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C76" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D76" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="77" ht="16.5" customHeight="1" spans="1:4">
       <c r="A77" s="23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B77" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C77" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D77" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="78" ht="16.5" customHeight="1" spans="2:4">
       <c r="B78" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C78" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D78" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C78" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D78" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="79" ht="16.5" customHeight="1" spans="2:4">
       <c r="B79" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C79" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D79" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="80" ht="16.5" customHeight="1" spans="1:4">
@@ -3981,71 +4114,71 @@
         <v>114</v>
       </c>
       <c r="B80" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C80" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D80" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="81" ht="16.5" customHeight="1" spans="2:4">
       <c r="B81" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C81" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D81" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C81" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D81" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="82" ht="16.5" customHeight="1" spans="2:4">
       <c r="B82" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C82" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D82" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="83" ht="16.5" customHeight="1" spans="1:4">
       <c r="A83" s="23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B83" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C83" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D83" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="84" ht="16.5" customHeight="1" spans="2:4">
       <c r="B84" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C84" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D84" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C84" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D84" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="85" ht="16.5" customHeight="1" spans="2:4">
       <c r="B85" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C85" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D85" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="86" ht="16.5" customHeight="1" spans="1:4">
@@ -4053,71 +4186,71 @@
         <v>115</v>
       </c>
       <c r="B86" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C86" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D86" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="87" ht="16.5" customHeight="1" spans="2:4">
       <c r="B87" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C87" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D87" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C87" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D87" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="88" ht="16.5" customHeight="1" spans="2:4">
       <c r="B88" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C88" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D88" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="89" ht="16.5" customHeight="1" spans="1:4">
       <c r="A89" s="23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B89" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C89" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D89" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="90" ht="16.5" customHeight="1" spans="2:4">
       <c r="B90" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C90" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D90" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C90" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D90" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="91" ht="16.5" customHeight="1" spans="2:4">
       <c r="B91" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C91" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D91" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="92" ht="16.5" customHeight="1" spans="1:4">
@@ -4125,71 +4258,71 @@
         <v>116</v>
       </c>
       <c r="B92" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C92" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D92" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="93" ht="16.5" customHeight="1" spans="2:4">
       <c r="B93" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C93" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D93" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C93" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D93" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="94" ht="16.5" customHeight="1" spans="2:4">
       <c r="B94" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C94" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D94" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="95" ht="16.5" customHeight="1" spans="1:4">
       <c r="A95" s="23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B95" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C95" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D95" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="96" ht="16.5" customHeight="1" spans="2:4">
       <c r="B96" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C96" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D96" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C96" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D96" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="97" ht="16.5" customHeight="1" spans="2:4">
       <c r="B97" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C97" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D97" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="98" ht="16.5" customHeight="1" spans="1:4">
@@ -4197,71 +4330,71 @@
         <v>117</v>
       </c>
       <c r="B98" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C98" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D98" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="99" ht="16.5" customHeight="1" spans="2:4">
       <c r="B99" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C99" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D99" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C99" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D99" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="100" ht="16.5" customHeight="1" spans="2:4">
       <c r="B100" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C100" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D100" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="101" ht="16.5" customHeight="1" spans="1:4">
       <c r="A101" s="23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B101" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C101" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D101" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="102" ht="16.5" customHeight="1" spans="2:4">
       <c r="B102" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C102" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D102" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C102" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D102" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="103" ht="16.5" customHeight="1" spans="2:4">
       <c r="B103" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C103" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D103" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="104" ht="16.5" customHeight="1" spans="1:4">
@@ -4269,71 +4402,71 @@
         <v>118</v>
       </c>
       <c r="B104" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C104" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D104" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="105" ht="16.5" customHeight="1" spans="2:4">
       <c r="B105" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C105" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D105" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C105" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D105" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="106" ht="16.5" customHeight="1" spans="2:4">
       <c r="B106" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C106" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D106" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="107" ht="16.5" customHeight="1" spans="1:4">
       <c r="A107" s="23" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B107" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C107" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D107" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="108" ht="16.5" customHeight="1" spans="2:4">
       <c r="B108" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C108" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D108" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C108" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D108" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="109" ht="16.5" customHeight="1" spans="2:4">
       <c r="B109" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C109" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D109" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="110" ht="16.5" customHeight="1" spans="1:4">
@@ -4341,71 +4474,71 @@
         <v>119</v>
       </c>
       <c r="B110" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C110" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D110" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="111" ht="16.5" customHeight="1" spans="2:4">
       <c r="B111" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C111" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D111" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C111" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D111" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="112" ht="16.5" customHeight="1" spans="2:4">
       <c r="B112" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C112" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D112" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="113" ht="16.5" customHeight="1" spans="1:4">
       <c r="A113" s="23" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B113" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C113" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D113" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="114" ht="16.5" customHeight="1" spans="2:4">
       <c r="B114" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C114" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D114" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C114" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D114" s="25" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="115" ht="16.5" customHeight="1" spans="2:4">
       <c r="B115" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C115" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D115" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -4480,52 +4613,52 @@
   <sheetData>
     <row r="1" ht="18.6" customHeight="1" spans="1:16">
       <c r="A1" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J1" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P1" s="15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" ht="18.6" customHeight="1" spans="1:16">
@@ -4536,43 +4669,43 @@
         <v>8</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H2" s="10" t="s">
         <v>12</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L2" s="14" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M2" s="14" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N2" s="14" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O2" s="14" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P2" s="16" t="s">
         <v>8</v>
@@ -4580,12 +4713,12 @@
     </row>
     <row r="3" ht="18.6" customHeight="1" spans="1:16">
       <c r="A3" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="10"/>
       <c r="D3" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E3" s="10"/>
       <c r="F3" s="10"/>
@@ -4602,69 +4735,69 @@
     </row>
     <row r="4" ht="18.6" customHeight="1" spans="1:16">
       <c r="A4" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M4" s="14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N4" s="14" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O4" s="14" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P4" s="18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" ht="18.6" customHeight="1" spans="1:16">
       <c r="A5" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B5" s="13">
         <v>101</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>22</v>
@@ -4705,13 +4838,13 @@
         <v>22</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F6" s="12" t="s">
         <v>28</v>
@@ -4726,7 +4859,7 @@
         <v>10</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K6" s="19">
         <v>0.1</v>
@@ -4752,13 +4885,13 @@
         <v>28</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>33</v>
@@ -4797,13 +4930,13 @@
         <v>33</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F8" s="12" t="s">
         <v>38</v>
@@ -4842,13 +4975,13 @@
         <v>38</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>41</v>
@@ -4863,7 +4996,7 @@
         <v>25</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K9" s="19">
         <v>0.1</v>
@@ -4889,16 +5022,16 @@
         <v>41</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G10" s="13">
         <v>30</v>
@@ -4910,7 +5043,7 @@
         <v>16</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K10" s="19">
         <v>0.1</v>
@@ -4933,19 +5066,19 @@
     </row>
     <row r="11" ht="18.6" customHeight="1" spans="1:16">
       <c r="A11" s="13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G11" s="13">
         <v>35</v>
@@ -4957,7 +5090,7 @@
         <v>14</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K11" s="19">
         <v>0.1</v>
@@ -4980,19 +5113,19 @@
     </row>
     <row r="12" ht="18.6" customHeight="1" spans="1:16">
       <c r="A12" s="13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G12" s="13">
         <v>40</v>
@@ -5004,7 +5137,7 @@
         <v>12</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K12" s="19">
         <v>0.1</v>
@@ -5027,19 +5160,19 @@
     </row>
     <row r="13" ht="18.6" customHeight="1" spans="1:16">
       <c r="A13" s="13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G13" s="13">
         <v>45</v>
@@ -5051,7 +5184,7 @@
         <v>10</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K13" s="19">
         <v>0.1</v>
@@ -5074,19 +5207,19 @@
     </row>
     <row r="14" ht="18.6" customHeight="1" spans="1:16">
       <c r="A14" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G14" s="13">
         <v>50</v>
@@ -5098,7 +5231,7 @@
         <v>8</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K14" s="19">
         <v>0.1</v>
@@ -5121,19 +5254,19 @@
     </row>
     <row r="15" ht="18.6" customHeight="1" spans="1:16">
       <c r="A15" s="13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G15" s="13">
         <v>55</v>
@@ -5145,7 +5278,7 @@
         <v>6</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K15" s="19">
         <v>0.1</v>
@@ -5168,19 +5301,19 @@
     </row>
     <row r="16" ht="18.6" customHeight="1" spans="1:16">
       <c r="A16" s="13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G16" s="13">
         <v>60</v>
@@ -5192,7 +5325,7 @@
         <v>4</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K16" s="19">
         <v>0</v>
@@ -5215,19 +5348,19 @@
     </row>
     <row r="17" ht="18.6" customHeight="1" spans="1:16">
       <c r="A17" s="13" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G17" s="13">
         <v>65</v>
@@ -5260,19 +5393,19 @@
     </row>
     <row r="18" ht="18.6" customHeight="1" spans="1:16">
       <c r="A18" s="13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G18" s="13">
         <v>70</v>
@@ -5305,19 +5438,19 @@
     </row>
     <row r="19" ht="18.6" customHeight="1" spans="1:16">
       <c r="A19" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G19" s="13">
         <v>75</v>
@@ -5350,19 +5483,19 @@
     </row>
     <row r="20" ht="18.6" customHeight="1" spans="1:16">
       <c r="A20" s="13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G20" s="13">
         <v>80</v>
@@ -5395,19 +5528,19 @@
     </row>
     <row r="21" ht="18.6" customHeight="1" spans="1:16">
       <c r="A21" s="13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G21" s="13">
         <v>100</v>
@@ -5440,19 +5573,19 @@
     </row>
     <row r="22" ht="18.6" customHeight="1" spans="1:16">
       <c r="A22" s="13" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G22" s="13">
         <v>120</v>
@@ -5461,7 +5594,7 @@
         <v>22</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J22" s="12"/>
       <c r="K22" s="19">
@@ -5485,19 +5618,19 @@
     </row>
     <row r="23" ht="18.6" customHeight="1" spans="1:16">
       <c r="A23" s="13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G23" s="13">
         <v>140</v>
@@ -5530,19 +5663,19 @@
     </row>
     <row r="24" ht="18.6" customHeight="1" spans="1:16">
       <c r="A24" s="13" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G24" s="13">
         <v>160</v>
@@ -5551,7 +5684,7 @@
         <v>22</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J24" s="12"/>
       <c r="K24" s="19">
@@ -5575,19 +5708,19 @@
     </row>
     <row r="25" ht="18.6" customHeight="1" spans="1:16">
       <c r="A25" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B25" s="13">
         <v>102</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F25" s="12" t="s">
         <v>22</v>
@@ -5599,10 +5732,10 @@
         <v>1</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J25" s="20" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K25" s="19">
         <v>0</v>
@@ -5628,13 +5761,13 @@
         <v>22</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F26" s="12" t="s">
         <v>28</v>
@@ -5649,7 +5782,7 @@
         <v>5</v>
       </c>
       <c r="J26" s="20" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K26" s="19">
         <v>0</v>
@@ -5675,13 +5808,13 @@
         <v>28</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F27" s="12" t="s">
         <v>33</v>
@@ -5693,10 +5826,10 @@
         <v>22</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J27" s="20" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K27" s="19">
         <v>0</v>
@@ -5722,13 +5855,13 @@
         <v>33</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F28" s="12" t="s">
         <v>38</v>
@@ -5740,10 +5873,10 @@
         <v>22</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J28" s="20" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K28" s="19">
         <v>0</v>
@@ -5769,13 +5902,13 @@
         <v>38</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F29" s="12" t="s">
         <v>41</v>
@@ -5790,7 +5923,7 @@
         <v>6</v>
       </c>
       <c r="J29" s="20" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K29" s="19">
         <v>0</v>
@@ -5816,16 +5949,16 @@
         <v>41</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G30" s="13">
         <v>30</v>
@@ -5834,10 +5967,10 @@
         <v>1</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J30" s="20" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K30" s="19">
         <v>0</v>
@@ -5860,19 +5993,19 @@
     </row>
     <row r="31" ht="18.6" customHeight="1" spans="1:16">
       <c r="A31" s="13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G31" s="13">
         <v>35</v>
@@ -5881,10 +6014,10 @@
         <v>1</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J31" s="20" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K31" s="19">
         <v>0</v>
@@ -5907,19 +6040,19 @@
     </row>
     <row r="32" ht="18.6" customHeight="1" spans="1:16">
       <c r="A32" s="13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G32" s="13">
         <v>40</v>
@@ -5931,7 +6064,7 @@
         <v>7</v>
       </c>
       <c r="J32" s="20" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K32" s="19">
         <v>0</v>
@@ -5954,19 +6087,19 @@
     </row>
     <row r="33" ht="18.6" customHeight="1" spans="1:16">
       <c r="A33" s="13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G33" s="13">
         <v>45</v>
@@ -5975,10 +6108,10 @@
         <v>22</v>
       </c>
       <c r="I33" s="13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J33" s="20" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K33" s="19">
         <v>0</v>
@@ -6001,19 +6134,19 @@
     </row>
     <row r="34" ht="18.6" customHeight="1" spans="1:16">
       <c r="A34" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G34" s="13">
         <v>50</v>
@@ -6022,10 +6155,10 @@
         <v>22</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J34" s="20" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K34" s="19">
         <v>0</v>
@@ -6048,19 +6181,19 @@
     </row>
     <row r="35" ht="18.6" customHeight="1" spans="1:16">
       <c r="A35" s="13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G35" s="13">
         <v>55</v>
@@ -6072,7 +6205,7 @@
         <v>8</v>
       </c>
       <c r="J35" s="20" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K35" s="19">
         <v>0</v>
@@ -6095,19 +6228,19 @@
     </row>
     <row r="36" ht="18.6" customHeight="1" spans="1:16">
       <c r="A36" s="13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G36" s="13">
         <v>60</v>
@@ -6116,10 +6249,10 @@
         <v>1</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J36" s="20" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K36" s="19">
         <v>0</v>
@@ -6142,19 +6275,19 @@
     </row>
     <row r="37" ht="18.6" customHeight="1" spans="1:16">
       <c r="A37" s="13" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G37" s="13">
         <v>65</v>
@@ -6163,10 +6296,10 @@
         <v>22</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J37" s="20" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K37" s="19">
         <v>0</v>
@@ -6189,19 +6322,19 @@
     </row>
     <row r="38" ht="18.6" customHeight="1" spans="1:16">
       <c r="A38" s="13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G38" s="13">
         <v>70</v>
@@ -6234,19 +6367,19 @@
     </row>
     <row r="39" ht="18.6" customHeight="1" spans="1:16">
       <c r="A39" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G39" s="13">
         <v>75</v>
@@ -6255,7 +6388,7 @@
         <v>22</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J39" s="12"/>
       <c r="K39" s="19">
@@ -6279,19 +6412,19 @@
     </row>
     <row r="40" ht="18.6" customHeight="1" spans="1:16">
       <c r="A40" s="13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G40" s="13">
         <v>80</v>
@@ -6300,7 +6433,7 @@
         <v>1</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J40" s="12"/>
       <c r="K40" s="19">
@@ -6324,19 +6457,19 @@
     </row>
     <row r="41" ht="18.6" customHeight="1" spans="1:16">
       <c r="A41" s="13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G41" s="13">
         <v>100</v>
@@ -6369,19 +6502,19 @@
     </row>
     <row r="42" ht="18.6" customHeight="1" spans="1:16">
       <c r="A42" s="13" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G42" s="13">
         <v>120</v>
@@ -6390,7 +6523,7 @@
         <v>22</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J42" s="12"/>
       <c r="K42" s="19">
@@ -6414,19 +6547,19 @@
     </row>
     <row r="43" ht="18.6" customHeight="1" spans="1:16">
       <c r="A43" s="13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G43" s="13">
         <v>140</v>
@@ -6435,7 +6568,7 @@
         <v>22</v>
       </c>
       <c r="I43" s="13" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J43" s="12"/>
       <c r="K43" s="19">
@@ -6459,19 +6592,19 @@
     </row>
     <row r="44" ht="18.6" customHeight="1" spans="1:16">
       <c r="A44" s="13" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G44" s="13">
         <v>160</v>
@@ -6504,16 +6637,16 @@
     </row>
     <row r="45" ht="18.6" customHeight="1" spans="1:16">
       <c r="A45" s="13" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F45" s="12" t="s">
         <v>22</v>
@@ -6525,7 +6658,7 @@
         <v>1</v>
       </c>
       <c r="I45" s="13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J45" s="12"/>
       <c r="K45" s="19">
@@ -6549,19 +6682,19 @@
     </row>
     <row r="46" ht="18.6" customHeight="1" spans="1:16">
       <c r="A46" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B46" s="13">
         <v>103</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F46" s="12" t="s">
         <v>28</v>
@@ -6573,7 +6706,7 @@
         <v>1</v>
       </c>
       <c r="I46" s="13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J46" s="12"/>
       <c r="K46" s="19">
@@ -6600,13 +6733,13 @@
         <v>22</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F47" s="12" t="s">
         <v>33</v>
@@ -6645,13 +6778,13 @@
         <v>28</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F48" s="12" t="s">
         <v>38</v>
@@ -6663,7 +6796,7 @@
         <v>22</v>
       </c>
       <c r="I48" s="13" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J48" s="12"/>
       <c r="K48" s="19">
@@ -6690,13 +6823,13 @@
         <v>33</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F49" s="12" t="s">
         <v>41</v>
@@ -6708,7 +6841,7 @@
         <v>22</v>
       </c>
       <c r="I49" s="13" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J49" s="12"/>
       <c r="K49" s="19">
@@ -6735,13 +6868,13 @@
         <v>38</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F50" s="12" t="s">
         <v>22</v>
@@ -6777,19 +6910,19 @@
     </row>
     <row r="51" ht="18.6" customHeight="1" spans="1:16">
       <c r="A51" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B51" s="13">
         <v>104</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F51" s="12" t="s">
         <v>28</v>
@@ -6801,7 +6934,7 @@
         <v>1</v>
       </c>
       <c r="I51" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J51" s="12"/>
       <c r="K51" s="19">
@@ -6828,13 +6961,13 @@
         <v>22</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F52" s="12" t="s">
         <v>33</v>
@@ -6846,7 +6979,7 @@
         <v>22</v>
       </c>
       <c r="I52" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J52" s="12"/>
       <c r="K52" s="19">
@@ -6873,13 +7006,13 @@
         <v>28</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F53" s="12" t="s">
         <v>38</v>
@@ -6918,13 +7051,13 @@
         <v>33</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F54" s="12" t="s">
         <v>41</v>
@@ -6936,7 +7069,7 @@
         <v>22</v>
       </c>
       <c r="I54" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J54" s="12"/>
       <c r="K54" s="19">
@@ -6963,13 +7096,13 @@
         <v>38</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F55" s="12" t="s">
         <v>22</v>
@@ -6981,7 +7114,7 @@
         <v>1</v>
       </c>
       <c r="I55" s="13" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J55" s="12"/>
       <c r="K55" s="19">
@@ -7005,19 +7138,19 @@
     </row>
     <row r="56" ht="18.6" customHeight="1" spans="1:16">
       <c r="A56" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B56" s="13">
         <v>105</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F56" s="12" t="s">
         <v>28</v>
@@ -7056,13 +7189,13 @@
         <v>22</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F57" s="12" t="s">
         <v>33</v>
@@ -7074,7 +7207,7 @@
         <v>22</v>
       </c>
       <c r="I57" s="13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J57" s="12"/>
       <c r="K57" s="19">
@@ -7101,13 +7234,13 @@
         <v>28</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F58" s="12" t="s">
         <v>38</v>
@@ -7119,7 +7252,7 @@
         <v>22</v>
       </c>
       <c r="I58" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J58" s="12"/>
       <c r="K58" s="19">
@@ -7146,13 +7279,13 @@
         <v>33</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F59" s="12" t="s">
         <v>41</v>
@@ -7191,13 +7324,13 @@
         <v>38</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F60" s="12" t="s">
         <v>22</v>
@@ -7209,7 +7342,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="13" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J60" s="12"/>
       <c r="K60" s="19">
@@ -7233,19 +7366,19 @@
     </row>
     <row r="61" ht="18.6" customHeight="1" spans="1:16">
       <c r="A61" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B61" s="13">
         <v>106</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F61" s="12" t="s">
         <v>28</v>
@@ -7257,7 +7390,7 @@
         <v>1</v>
       </c>
       <c r="I61" s="13" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J61" s="12"/>
       <c r="K61" s="19">
@@ -7284,13 +7417,13 @@
         <v>22</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F62" s="12" t="s">
         <v>33</v>
@@ -7329,13 +7462,13 @@
         <v>28</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F63" s="12" t="s">
         <v>38</v>
@@ -7347,7 +7480,7 @@
         <v>22</v>
       </c>
       <c r="I63" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J63" s="12"/>
       <c r="K63" s="19">
@@ -7374,13 +7507,13 @@
         <v>33</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F64" s="12" t="s">
         <v>41</v>
@@ -7392,7 +7525,7 @@
         <v>22</v>
       </c>
       <c r="I64" s="13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J64" s="12"/>
       <c r="K64" s="19">
@@ -7419,13 +7552,13 @@
         <v>38</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F65" s="12" t="s">
         <v>22</v>
@@ -7461,19 +7594,19 @@
     </row>
     <row r="66" ht="18.6" customHeight="1" spans="1:16">
       <c r="A66" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B66" s="13">
         <v>107</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F66" s="12" t="s">
         <v>28</v>
@@ -7485,7 +7618,7 @@
         <v>1</v>
       </c>
       <c r="I66" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J66" s="12"/>
       <c r="K66" s="19">
@@ -7512,13 +7645,13 @@
         <v>22</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F67" s="12" t="s">
         <v>33</v>
@@ -7530,7 +7663,7 @@
         <v>22</v>
       </c>
       <c r="I67" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="J67" s="12"/>
       <c r="K67" s="19">
@@ -7557,13 +7690,13 @@
         <v>28</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F68" s="12" t="s">
         <v>38</v>
@@ -7602,13 +7735,13 @@
         <v>33</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F69" s="12" t="s">
         <v>41</v>
@@ -7620,7 +7753,7 @@
         <v>22</v>
       </c>
       <c r="I69" s="13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J69" s="12"/>
       <c r="K69" s="19">
@@ -7647,13 +7780,13 @@
         <v>38</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F70" s="12" t="s">
         <v>22</v>
@@ -7665,7 +7798,7 @@
         <v>1</v>
       </c>
       <c r="I70" s="13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J70" s="12"/>
       <c r="K70" s="19">
@@ -7689,19 +7822,19 @@
     </row>
     <row r="71" ht="18.6" customHeight="1" spans="1:16">
       <c r="A71" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B71" s="13">
         <v>108</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F71" s="12" t="s">
         <v>28</v>
@@ -7740,13 +7873,13 @@
         <v>22</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F72" s="12" t="s">
         <v>33</v>
@@ -7758,7 +7891,7 @@
         <v>22</v>
       </c>
       <c r="I72" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J72" s="12"/>
       <c r="K72" s="19">
@@ -7785,13 +7918,13 @@
         <v>28</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F73" s="12" t="s">
         <v>38</v>
@@ -7803,7 +7936,7 @@
         <v>22</v>
       </c>
       <c r="I73" s="13" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J73" s="12"/>
       <c r="K73" s="19">
@@ -7830,13 +7963,13 @@
         <v>33</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F74" s="12" t="s">
         <v>41</v>
@@ -7875,13 +8008,13 @@
         <v>38</v>
       </c>
       <c r="C75" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F75" s="12" t="s">
         <v>22</v>
@@ -7893,7 +8026,7 @@
         <v>1</v>
       </c>
       <c r="I75" s="13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J75" s="12"/>
       <c r="K75" s="19">
@@ -7917,19 +8050,19 @@
     </row>
     <row r="76" ht="18.6" customHeight="1" spans="1:16">
       <c r="A76" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B76" s="13">
         <v>109</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F76" s="12" t="s">
         <v>28</v>
@@ -7941,7 +8074,7 @@
         <v>1</v>
       </c>
       <c r="I76" s="13" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J76" s="12"/>
       <c r="K76" s="19">
@@ -7968,13 +8101,13 @@
         <v>22</v>
       </c>
       <c r="C77" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F77" s="12" t="s">
         <v>33</v>
@@ -8013,13 +8146,13 @@
         <v>28</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D78" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F78" s="12" t="s">
         <v>38</v>
@@ -8031,7 +8164,7 @@
         <v>22</v>
       </c>
       <c r="I78" s="13" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J78" s="12"/>
       <c r="K78" s="19">
@@ -8058,13 +8191,13 @@
         <v>33</v>
       </c>
       <c r="C79" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F79" s="12" t="s">
         <v>41</v>
@@ -8076,7 +8209,7 @@
         <v>22</v>
       </c>
       <c r="I79" s="13" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J79" s="12"/>
       <c r="K79" s="19">
@@ -8103,13 +8236,13 @@
         <v>38</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F80" s="12" t="s">
         <v>22</v>
@@ -8145,19 +8278,19 @@
     </row>
     <row r="81" ht="18.6" customHeight="1" spans="1:16">
       <c r="A81" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B81" s="13">
         <v>110</v>
       </c>
       <c r="C81" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F81" s="12" t="s">
         <v>28</v>
@@ -8169,7 +8302,7 @@
         <v>1</v>
       </c>
       <c r="I81" s="13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J81" s="12"/>
       <c r="K81" s="19">
@@ -8196,13 +8329,13 @@
         <v>22</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D82" s="12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F82" s="12" t="s">
         <v>33</v>
@@ -8214,7 +8347,7 @@
         <v>22</v>
       </c>
       <c r="I82" s="13" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J82" s="12"/>
       <c r="K82" s="19">
@@ -8241,13 +8374,13 @@
         <v>28</v>
       </c>
       <c r="C83" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F83" s="12" t="s">
         <v>38</v>
@@ -8286,13 +8419,13 @@
         <v>33</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F84" s="12" t="s">
         <v>41</v>
@@ -8304,7 +8437,7 @@
         <v>22</v>
       </c>
       <c r="I84" s="13" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J84" s="12"/>
       <c r="K84" s="19">
@@ -8331,13 +8464,13 @@
         <v>38</v>
       </c>
       <c r="C85" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F85" s="12" t="s">
         <v>22</v>
@@ -8349,7 +8482,7 @@
         <v>1</v>
       </c>
       <c r="I85" s="13" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J85" s="12"/>
       <c r="K85" s="19">
@@ -8373,19 +8506,19 @@
     </row>
     <row r="86" ht="18.6" customHeight="1" spans="1:16">
       <c r="A86" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B86" s="13">
         <v>111</v>
       </c>
       <c r="C86" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D86" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E86" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F86" s="12" t="s">
         <v>28</v>
@@ -8424,13 +8557,13 @@
         <v>22</v>
       </c>
       <c r="C87" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F87" s="12" t="s">
         <v>33</v>
@@ -8442,7 +8575,7 @@
         <v>22</v>
       </c>
       <c r="I87" s="13" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="J87" s="12"/>
       <c r="K87" s="19">
@@ -8469,13 +8602,13 @@
         <v>28</v>
       </c>
       <c r="C88" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F88" s="12" t="s">
         <v>38</v>
@@ -8487,7 +8620,7 @@
         <v>22</v>
       </c>
       <c r="I88" s="13" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J88" s="12"/>
       <c r="K88" s="19">
@@ -8514,13 +8647,13 @@
         <v>33</v>
       </c>
       <c r="C89" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F89" s="12" t="s">
         <v>41</v>
@@ -8559,13 +8692,13 @@
         <v>38</v>
       </c>
       <c r="C90" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D90" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F90" s="12" t="s">
         <v>22</v>
@@ -8577,7 +8710,7 @@
         <v>1</v>
       </c>
       <c r="I90" s="13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J90" s="12"/>
       <c r="K90" s="19">
@@ -8601,19 +8734,19 @@
     </row>
     <row r="91" ht="18.6" customHeight="1" spans="1:16">
       <c r="A91" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B91" s="13">
         <v>112</v>
       </c>
       <c r="C91" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F91" s="12" t="s">
         <v>28</v>
@@ -8625,7 +8758,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J91" s="12"/>
       <c r="K91" s="19">
@@ -8652,13 +8785,13 @@
         <v>22</v>
       </c>
       <c r="C92" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D92" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F92" s="12" t="s">
         <v>33</v>
@@ -8697,13 +8830,13 @@
         <v>28</v>
       </c>
       <c r="C93" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E93" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F93" s="12" t="s">
         <v>38</v>
@@ -8715,7 +8848,7 @@
         <v>22</v>
       </c>
       <c r="I93" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J93" s="12"/>
       <c r="K93" s="19">
@@ -8742,13 +8875,13 @@
         <v>33</v>
       </c>
       <c r="C94" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D94" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E94" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F94" s="12" t="s">
         <v>41</v>
@@ -8760,7 +8893,7 @@
         <v>22</v>
       </c>
       <c r="I94" s="13" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J94" s="12"/>
       <c r="K94" s="19">
@@ -8787,13 +8920,13 @@
         <v>38</v>
       </c>
       <c r="C95" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E95" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F95" s="12" t="s">
         <v>22</v>
@@ -8829,19 +8962,19 @@
     </row>
     <row r="96" ht="18.6" customHeight="1" spans="1:16">
       <c r="A96" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B96" s="13">
         <v>113</v>
       </c>
       <c r="C96" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D96" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E96" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F96" s="12" t="s">
         <v>28</v>
@@ -8853,7 +8986,7 @@
         <v>1</v>
       </c>
       <c r="I96" s="13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J96" s="12"/>
       <c r="K96" s="19">
@@ -8880,13 +9013,13 @@
         <v>22</v>
       </c>
       <c r="C97" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D97" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E97" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F97" s="12" t="s">
         <v>33</v>
@@ -8898,7 +9031,7 @@
         <v>22</v>
       </c>
       <c r="I97" s="13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J97" s="12"/>
       <c r="K97" s="19">
@@ -8925,13 +9058,13 @@
         <v>28</v>
       </c>
       <c r="C98" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D98" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E98" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F98" s="12" t="s">
         <v>38</v>
@@ -8970,13 +9103,13 @@
         <v>33</v>
       </c>
       <c r="C99" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D99" s="12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E99" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F99" s="12" t="s">
         <v>41</v>
@@ -8988,7 +9121,7 @@
         <v>22</v>
       </c>
       <c r="I99" s="13" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="J99" s="12"/>
       <c r="K99" s="19">
@@ -9015,13 +9148,13 @@
         <v>38</v>
       </c>
       <c r="C100" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D100" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E100" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F100" s="12" t="s">
         <v>22</v>
@@ -9033,7 +9166,7 @@
         <v>1</v>
       </c>
       <c r="I100" s="13" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J100" s="12"/>
       <c r="K100" s="19">
@@ -9057,19 +9190,19 @@
     </row>
     <row r="101" ht="18.6" customHeight="1" spans="1:16">
       <c r="A101" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B101" s="13">
         <v>114</v>
       </c>
       <c r="C101" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D101" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E101" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F101" s="12" t="s">
         <v>28</v>
@@ -9108,13 +9241,13 @@
         <v>22</v>
       </c>
       <c r="C102" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D102" s="12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F102" s="12" t="s">
         <v>33</v>
@@ -9126,7 +9259,7 @@
         <v>22</v>
       </c>
       <c r="I102" s="13" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J102" s="12"/>
       <c r="K102" s="19">
@@ -9153,13 +9286,13 @@
         <v>28</v>
       </c>
       <c r="C103" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D103" s="12" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F103" s="12" t="s">
         <v>38</v>
@@ -9171,7 +9304,7 @@
         <v>22</v>
       </c>
       <c r="I103" s="13" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J103" s="12"/>
       <c r="K103" s="19">
@@ -9198,13 +9331,13 @@
         <v>33</v>
       </c>
       <c r="C104" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D104" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E104" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F104" s="12" t="s">
         <v>41</v>
@@ -9243,13 +9376,13 @@
         <v>38</v>
       </c>
       <c r="C105" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D105" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E105" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F105" s="12" t="s">
         <v>22</v>
@@ -9261,7 +9394,7 @@
         <v>1</v>
       </c>
       <c r="I105" s="13" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J105" s="12"/>
       <c r="K105" s="19">
@@ -9285,19 +9418,19 @@
     </row>
     <row r="106" ht="18.6" customHeight="1" spans="1:16">
       <c r="A106" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B106" s="13">
         <v>115</v>
       </c>
       <c r="C106" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D106" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E106" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F106" s="12" t="s">
         <v>28</v>
@@ -9309,7 +9442,7 @@
         <v>1</v>
       </c>
       <c r="I106" s="13" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J106" s="12"/>
       <c r="K106" s="19">
@@ -9336,13 +9469,13 @@
         <v>22</v>
       </c>
       <c r="C107" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D107" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E107" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F107" s="12" t="s">
         <v>33</v>
@@ -9381,13 +9514,13 @@
         <v>28</v>
       </c>
       <c r="C108" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D108" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E108" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F108" s="12" t="s">
         <v>38</v>
@@ -9399,7 +9532,7 @@
         <v>22</v>
       </c>
       <c r="I108" s="13" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J108" s="12"/>
       <c r="K108" s="19">
@@ -9426,13 +9559,13 @@
         <v>33</v>
       </c>
       <c r="C109" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D109" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E109" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F109" s="12" t="s">
         <v>41</v>
@@ -9444,7 +9577,7 @@
         <v>22</v>
       </c>
       <c r="I109" s="13" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J109" s="12"/>
       <c r="K109" s="19">
@@ -9471,13 +9604,13 @@
         <v>38</v>
       </c>
       <c r="C110" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D110" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E110" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F110" s="12" t="s">
         <v>22</v>
@@ -9513,19 +9646,19 @@
     </row>
     <row r="111" ht="18.6" customHeight="1" spans="1:16">
       <c r="A111" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B111" s="13">
         <v>116</v>
       </c>
       <c r="C111" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D111" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E111" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F111" s="12" t="s">
         <v>28</v>
@@ -9537,7 +9670,7 @@
         <v>1</v>
       </c>
       <c r="I111" s="13" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J111" s="12"/>
       <c r="K111" s="19">
@@ -9564,13 +9697,13 @@
         <v>22</v>
       </c>
       <c r="C112" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D112" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E112" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F112" s="12" t="s">
         <v>33</v>
@@ -9582,7 +9715,7 @@
         <v>22</v>
       </c>
       <c r="I112" s="13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J112" s="12"/>
       <c r="K112" s="19">
@@ -9609,13 +9742,13 @@
         <v>28</v>
       </c>
       <c r="C113" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D113" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E113" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F113" s="12" t="s">
         <v>38</v>
@@ -9654,13 +9787,13 @@
         <v>33</v>
       </c>
       <c r="C114" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D114" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E114" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F114" s="12" t="s">
         <v>41</v>
@@ -9672,7 +9805,7 @@
         <v>22</v>
       </c>
       <c r="I114" s="13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J114" s="12"/>
       <c r="K114" s="19">
@@ -9699,13 +9832,13 @@
         <v>38</v>
       </c>
       <c r="C115" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D115" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E115" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F115" s="12" t="s">
         <v>22</v>
@@ -9717,7 +9850,7 @@
         <v>1</v>
       </c>
       <c r="I115" s="13" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J115" s="12"/>
       <c r="K115" s="19">
@@ -9741,19 +9874,19 @@
     </row>
     <row r="116" ht="18.6" customHeight="1" spans="1:16">
       <c r="A116" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B116" s="13">
         <v>117</v>
       </c>
       <c r="C116" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D116" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E116" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F116" s="12" t="s">
         <v>28</v>
@@ -9792,13 +9925,13 @@
         <v>22</v>
       </c>
       <c r="C117" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D117" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E117" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F117" s="12" t="s">
         <v>33</v>
@@ -9810,7 +9943,7 @@
         <v>22</v>
       </c>
       <c r="I117" s="13" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J117" s="12"/>
       <c r="K117" s="19">
@@ -9837,13 +9970,13 @@
         <v>28</v>
       </c>
       <c r="C118" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D118" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E118" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F118" s="12" t="s">
         <v>38</v>
@@ -9855,7 +9988,7 @@
         <v>22</v>
       </c>
       <c r="I118" s="13" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J118" s="12"/>
       <c r="K118" s="19">
@@ -9882,13 +10015,13 @@
         <v>33</v>
       </c>
       <c r="C119" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D119" s="12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F119" s="12" t="s">
         <v>41</v>
@@ -9927,13 +10060,13 @@
         <v>38</v>
       </c>
       <c r="C120" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D120" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F120" s="12" t="s">
         <v>22</v>
@@ -9945,7 +10078,7 @@
         <v>1</v>
       </c>
       <c r="I120" s="13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J120" s="12"/>
       <c r="K120" s="19">
@@ -9969,19 +10102,19 @@
     </row>
     <row r="121" ht="18.6" customHeight="1" spans="1:16">
       <c r="A121" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B121" s="13">
         <v>118</v>
       </c>
       <c r="C121" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D121" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E121" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F121" s="12" t="s">
         <v>28</v>
@@ -9993,7 +10126,7 @@
         <v>1</v>
       </c>
       <c r="I121" s="13" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J121" s="12"/>
       <c r="K121" s="19">
@@ -10020,13 +10153,13 @@
         <v>22</v>
       </c>
       <c r="C122" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D122" s="12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E122" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F122" s="12" t="s">
         <v>33</v>
@@ -10065,13 +10198,13 @@
         <v>28</v>
       </c>
       <c r="C123" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D123" s="12" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E123" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F123" s="12" t="s">
         <v>38</v>
@@ -10083,7 +10216,7 @@
         <v>22</v>
       </c>
       <c r="I123" s="13" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J123" s="12"/>
       <c r="K123" s="19">
@@ -10110,13 +10243,13 @@
         <v>33</v>
       </c>
       <c r="C124" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D124" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E124" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F124" s="12" t="s">
         <v>41</v>
@@ -10128,7 +10261,7 @@
         <v>22</v>
       </c>
       <c r="I124" s="13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J124" s="12"/>
       <c r="K124" s="19">
@@ -10155,13 +10288,13 @@
         <v>38</v>
       </c>
       <c r="C125" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D125" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E125" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F125" s="12" t="s">
         <v>22</v>
@@ -10197,19 +10330,19 @@
     </row>
     <row r="126" ht="18.6" customHeight="1" spans="1:16">
       <c r="A126" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B126" s="13">
         <v>119</v>
       </c>
       <c r="C126" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D126" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E126" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F126" s="12" t="s">
         <v>28</v>
@@ -10221,7 +10354,7 @@
         <v>1</v>
       </c>
       <c r="I126" s="13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J126" s="12"/>
       <c r="K126" s="19">
@@ -10248,13 +10381,13 @@
         <v>22</v>
       </c>
       <c r="C127" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D127" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E127" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F127" s="12" t="s">
         <v>33</v>
@@ -10266,7 +10399,7 @@
         <v>22</v>
       </c>
       <c r="I127" s="13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J127" s="12"/>
       <c r="K127" s="19">
@@ -10293,13 +10426,13 @@
         <v>28</v>
       </c>
       <c r="C128" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D128" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E128" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F128" s="12" t="s">
         <v>38</v>
@@ -10338,13 +10471,13 @@
         <v>33</v>
       </c>
       <c r="C129" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D129" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E129" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F129" s="12" t="s">
         <v>41</v>
@@ -10356,7 +10489,7 @@
         <v>22</v>
       </c>
       <c r="I129" s="13" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J129" s="12"/>
       <c r="K129" s="19">
@@ -10383,13 +10516,13 @@
         <v>38</v>
       </c>
       <c r="C130" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D130" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E130" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F130" s="12" t="s">
         <v>22</v>
@@ -10401,7 +10534,7 @@
         <v>1</v>
       </c>
       <c r="I130" s="13" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J130" s="12"/>
       <c r="K130" s="19">
@@ -10425,19 +10558,19 @@
     </row>
     <row r="131" ht="18.6" customHeight="1" spans="1:16">
       <c r="A131" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B131" s="13">
         <v>120</v>
       </c>
       <c r="C131" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D131" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E131" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F131" s="12" t="s">
         <v>28</v>
@@ -10476,13 +10609,13 @@
         <v>22</v>
       </c>
       <c r="C132" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D132" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E132" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F132" s="12" t="s">
         <v>33</v>
@@ -10494,7 +10627,7 @@
         <v>22</v>
       </c>
       <c r="I132" s="13" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J132" s="12"/>
       <c r="K132" s="19">
@@ -10521,13 +10654,13 @@
         <v>28</v>
       </c>
       <c r="C133" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D133" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E133" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F133" s="12" t="s">
         <v>38</v>
@@ -10539,7 +10672,7 @@
         <v>22</v>
       </c>
       <c r="I133" s="13" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J133" s="12"/>
       <c r="K133" s="19">
@@ -10566,13 +10699,13 @@
         <v>33</v>
       </c>
       <c r="C134" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D134" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E134" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F134" s="12" t="s">
         <v>41</v>
@@ -10611,16 +10744,16 @@
         <v>38</v>
       </c>
       <c r="C135" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D135" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E135" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F135" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G135" s="13">
         <v>25</v>
@@ -10629,7 +10762,7 @@
         <v>1</v>
       </c>
       <c r="I135" s="13" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J135" s="12"/>
       <c r="K135" s="19">
@@ -10691,7 +10824,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -10701,12 +10834,12 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -10741,22 +10874,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:7">
@@ -10798,22 +10931,22 @@
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:7">
